--- a/etapa-calcul-1/CCA_Calcul1_Dinamica_GT63.xlsx
+++ b/etapa-calcul-1/CCA_Calcul1_Dinamica_GT63.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" name="A_f" vbProcedure="false">'Date de intrare'!$C$10</definedName>
-    <definedName function="false" hidden="false" name="a_med" vbProcedure="false">'Date de intrare'!$C$35</definedName>
+    <definedName function="false" hidden="false" name="a_med" vbProcedure="false">'Date de intrare'!$C$36</definedName>
     <definedName function="false" hidden="false" name="B_anv" vbProcedure="false">'Date de intrare'!$C$19</definedName>
     <definedName function="false" hidden="false" name="C_x" vbProcedure="false">'Date de intrare'!$C$9</definedName>
     <definedName function="false" hidden="false" name="delta_m" vbProcedure="false">'Date de intrare'!$C$26</definedName>
@@ -32,18 +32,19 @@
     <definedName function="false" hidden="false" name="M_DIN" vbProcedure="false">'Date de intrare'!$C$6</definedName>
     <definedName function="false" hidden="false" name="m_sofer" vbProcedure="false">'Date de intrare'!$C$7</definedName>
     <definedName function="false" hidden="false" name="n_m_vmax" vbProcedure="false">'Date de intrare'!$C$23</definedName>
-    <definedName function="false" hidden="false" name="p_1" vbProcedure="false">'Date de intrare'!$C$36</definedName>
+    <definedName function="false" hidden="false" name="p_1" vbProcedure="false">'Date de intrare'!$C$37</definedName>
+    <definedName function="false" hidden="false" name="P_cal" vbProcedure="false">'Date de intrare'!$C$33</definedName>
     <definedName function="false" hidden="false" name="P_cont" vbProcedure="false">'Date de intrare'!$C$13</definedName>
-    <definedName function="false" hidden="false" name="p_max" vbProcedure="false">'Date de intrare'!$C$38</definedName>
+    <definedName function="false" hidden="false" name="p_max" vbProcedure="false">'Date de intrare'!$C$39</definedName>
     <definedName function="false" hidden="false" name="P_vf" vbProcedure="false">'Date de intrare'!$C$12</definedName>
     <definedName function="false" hidden="false" name="rho_aer" vbProcedure="false">'Date de intrare'!$C$29</definedName>
     <definedName function="false" hidden="false" name="r_w" vbProcedure="false">'Date de intrare'!$C$22</definedName>
     <definedName function="false" hidden="false" name="t_200" vbProcedure="false">'Date de intrare'!$C$16</definedName>
     <definedName function="false" hidden="false" name="t_acc" vbProcedure="false">'Date de intrare'!$C$15</definedName>
     <definedName function="false" hidden="false" name="T_max" vbProcedure="false">'Date de intrare'!$C$11</definedName>
-    <definedName function="false" hidden="false" name="v_acc" vbProcedure="false">'Date de intrare'!$C$34</definedName>
+    <definedName function="false" hidden="false" name="v_acc" vbProcedure="false">'Date de intrare'!$C$35</definedName>
     <definedName function="false" hidden="false" name="v_max" vbProcedure="false">'Date de intrare'!$C$14</definedName>
-    <definedName function="false" hidden="false" name="v_p1" vbProcedure="false">'Date de intrare'!$C$37</definedName>
+    <definedName function="false" hidden="false" name="v_p1" vbProcedure="false">'Date de intrare'!$C$38</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -55,12 +56,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="296">
-  <si>
-    <t xml:space="preserve">Etapa 1 de calcul – rezultate: dinamica longitudinală a Mercedes-AMG GT 63 4-Door Coupé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calcul după „Noțiuni generale de dinamica vehiculului” (curs CCA C1, L. Popescu, UPB). Toate valorile sunt formule legate de foile „Date de intrare” și „Calcul regimuri”.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="267">
+  <si>
+    <t xml:space="preserve">Etapa 1 de calcul – rezultate: dinamica longitudinală a autoturismului electric Mercedes-AMG GT 63 4MATIC+ 4-Door Coupé (AMG.EA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calcul după „Noțiuni generale de dinamica vehiculului” (curs CCA C1, L. Popescu, UPB). Toate valorile sunt formule legate de foile „Date de intrare”, „Calcul regimuri” și „Caracteristica tractiune”.</t>
   </si>
   <si>
     <t xml:space="preserve">1. Date principale</t>
@@ -78,7 +79,7 @@
     <t xml:space="preserve">m²</t>
   </si>
   <si>
-    <t xml:space="preserve">Coeficient de rulare f / aderență μ</t>
+    <t xml:space="preserve">Coeficient de rezistență la rulare f / de aderență μ</t>
   </si>
   <si>
     <t xml:space="preserve">–</t>
@@ -141,39 +142,24 @@
     <t xml:space="preserve">Verificare (43)</t>
   </si>
   <si>
-    <t xml:space="preserve">Limitare</t>
+    <t xml:space="preserve">Limita activă</t>
   </si>
   <si>
     <t xml:space="preserve">S1</t>
   </si>
   <si>
-    <t xml:space="preserve">Viteză maximă, drum orizontal</t>
-  </si>
-  <si>
     <t xml:space="preserve">S2a</t>
   </si>
   <si>
-    <t xml:space="preserve">Accelerare 0–100 km/h – la pornire (v = 0)</t>
-  </si>
-  <si>
     <t xml:space="preserve">S2b</t>
   </si>
   <si>
-    <t xml:space="preserve">Accelerare 0–100 km/h – la 100 km/h</t>
-  </si>
-  <si>
     <t xml:space="preserve">S3</t>
   </si>
   <si>
-    <t xml:space="preserve">Rampă 10 % la 100 km/h, viteză constantă</t>
-  </si>
-  <si>
     <t xml:space="preserve">S4</t>
   </si>
   <si>
-    <t xml:space="preserve">Pornire pe panta maximă 30 % (v ≈ 0, a = 0)</t>
-  </si>
-  <si>
     <t xml:space="preserve">3. Indicatori de performanță (model vs. date oficiale)</t>
   </si>
   <si>
@@ -189,61 +175,16 @@
     <t xml:space="preserve">Observație</t>
   </si>
   <si>
-    <t xml:space="preserve">Timp 0–100 km/h, μ = 0,85 (asfalt uscat, tabel curs)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aderența limitează accelerarea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Timp 0–100 km/h, μ = 1,20 (anvelope de performanță)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">verifică performanța oficială</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Timp 0–200 km/h, μ = 1,20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">peste ≈100 km/h limitează puterea de vârf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accelerația maximă la pornire, μ = 0,85 [m/s²]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">oficial = accelerația medie 0–100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coeficient de aderență necesar pentru 0–100 în 2,4 s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regimul S2a</t>
-  </si>
-  <si>
     <t xml:space="preserve">Viteza maximă teoretică cu puterea continuă [km/h]</t>
   </si>
   <si>
-    <t xml:space="preserve">v_max reală este limitată electronic / de turație</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panta maximă (limită de aderență, μ = 0,85) [%]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tracțiune integrală</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puterea motoarelor la v_max = 300 km/h [kW]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comparată cu puterea continuă</t>
-  </si>
-  <si>
     <t xml:space="preserve">4. Concluzii</t>
   </si>
   <si>
     <t xml:space="preserve">Etapa 1 de calcul – dinamica longitudinală: date de intrare</t>
   </si>
   <si>
-    <t xml:space="preserve">Vehicul: Mercedes-AMG GT 63 4MATIC+ 4-Door Coupé (versiunea de serie a Concept AMG GT XX). Text albastru = valoare introdusă (modificabilă); text negru = formulă. Numele din coloana A pot fi folosite direct în formule (ex. =0,5*rho_aer*C_x*A_f*v^2).</t>
+    <t xml:space="preserve">Vehicul: Mercedes-AMG GT 63 4MATIC+ 4-Door Coupé (versiunea de serie a Concept AMG GT XX). Text albastru = valoare introdusă (modificabilă); text negru = formulă. Numele din coloana A pot fi folosite direct în formule; de exemplu, în foaia „Calcul regimuri” F_ra = ½·ρ·Cx·S·v² este =0.5*rho_aer*C_x*A_f*E7^2.</t>
   </si>
   <si>
     <t xml:space="preserve">Nume</t>
@@ -288,7 +229,7 @@
     <t xml:space="preserve">ipoteză</t>
   </si>
   <si>
-    <t xml:space="preserve">Regulamentul UE 1230/2012: masa în ordine de mers include șoferul de 75 kg</t>
+    <t xml:space="preserve">Regulamentul de punere în aplicare (UE) 2021/535 (anterior 1230/2012): masa în ordine de mers include șoferul de 75 kg</t>
   </si>
   <si>
     <t xml:space="preserve">M_calc</t>
@@ -426,7 +367,7 @@
     <t xml:space="preserve">r_w</t>
   </si>
   <si>
-    <t xml:space="preserve">Raza liberă = D_jantă/2 + B·h/B; r_w = k_def × raza liberă</t>
+    <t xml:space="preserve">Raza liberă = D_jant·25,4/2 + B_anv·h_rap [mm]; r_w = k_def × raza liberă / 1000 [m]</t>
   </si>
   <si>
     <t xml:space="preserve">n_m_vmax</t>
@@ -447,7 +388,7 @@
     <t xml:space="preserve">Raportul total de transmitere i_g (punte spate, estimat)</t>
   </si>
   <si>
-    <t xml:space="preserve">Raportul nu este publicat: i_g = n_motor / n_roată la v_max (limită inferioară). Se folosește ca raport echivalent pentru întreaga acționare.</t>
+    <t xml:space="preserve">Raportul nu este publicat: i_g = n_m / n_w la v_max (limită inferioară, turația oficială fiind „peste 13 000”). Se folosește ca raport echivalent pentru întreaga acționare. Deoarece i_g se calculează din r_w, raportul i_g/r_w este fix: forțele, puterile și timpii nu depind de r_w (doar T_w și n_w).</t>
   </si>
   <si>
     <t xml:space="preserve">eta_t</t>
@@ -522,7 +463,19 @@
     <t xml:space="preserve">Coeficientul de aderență μ – anvelope de performanță</t>
   </si>
   <si>
-    <t xml:space="preserve">Anvelope sport de înaltă aderență pe asfalt uscat, cald (verificare a performanței oficiale)</t>
+    <t xml:space="preserve">calibrare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valoare de calibrare: μ necesar pentru 0–100 km/h în 2,4 s este 1,19 (regimul S2a). Depășește tabelul cursului (asfalt uscat 0,80–0,90) – realizabil doar cu anvelope sport pe asfalt uscat, cald.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P_cal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puterea medie disponibilă care reproduce 0–200 km/h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aleasă astfel încât modelul (μ = 1,20) să dea 0–200 km/h ≈ 6,8 s – foaia „Caracteristica tractiune”, coloanele V–X. Arată că cei 860 kW nu sunt disponibili integral pe tot intervalul 100–200 km/h.</t>
   </si>
   <si>
     <t xml:space="preserve">Cerințe de calcul (regimuri)</t>
@@ -564,7 +517,7 @@
     <t xml:space="preserve">Viteza constantă pe panta p_1</t>
   </si>
   <si>
-    <t xml:space="preserve">Deplasare pe autostradă în rampă</t>
+    <t xml:space="preserve">Drum național / montan în rampă; panta de 10 % este exemplul din curs, rel. (21)</t>
   </si>
   <si>
     <t xml:space="preserve">p_max</t>
@@ -576,22 +529,25 @@
     <t xml:space="preserve">Cerință uzuală pentru autoturisme (rampe de parcare); se precizează în tema de proiectare</t>
   </si>
   <si>
-    <t xml:space="preserve">Ipoteze ale modelului (curs C1, cap. 1):</t>
+    <t xml:space="preserve">Ipoteze ale modelului (curs C1):</t>
   </si>
   <si>
     <t xml:space="preserve">1. Model longitudinal simplificat: vehiculul este un corp rigid care se deplasează pe direcția pantei; vânt nul (rel. 7, nu rel. 8).</t>
   </si>
   <si>
-    <t xml:space="preserve">2. Tracțiune integrală (3 motoare, 2 spate + 1 față): întreaga greutate este pe roți motoare, deci F_z = M·g·cos α (rel. 37), fără transfer de sarcină între punți.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Acționarea este tratată ca un motor echivalent cu cuplul T_m,max și raportul i_g; F_t,drive = min(T_m,max·i_g·η/r_w ; η·P/v) (rel. 6 și 30).</t>
+    <t xml:space="preserve">2. Tracțiune integrală (3 motoare: 2 spate + 1 față) cu distribuție ideală a cuplului între punți, proporțională cu sarcina dinamică a fiecărei punți (rel. 39); suma sarcinilor normale este F_z = M·g·cos α (rel. 37). Verificarea pe punți (înălțimea centrului de greutate, rapoartele față/spate – cap. 10) rămâne pentru etapa următoare.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Acționarea este tratată ca un motor echivalent cu cuplul T_m,max și raportul i_g: F_t,drive = min(T_m,max·i_g·η/r_w ; η·P/v) (rel. 6 și 30), folosit în (40).</t>
   </si>
   <si>
     <t xml:space="preserve">4. f și μ sunt considerați constanți (nivelul „simplificat” din tabelul cursului: dimensionare preliminară).</t>
   </si>
   <si>
-    <t xml:space="preserve">Calculul regimurilor caracteristice – relațiile din curs C1</t>
+    <t xml:space="preserve">5. Masele în rotație (δ, rel. 23): la limita de aderență forța din contactul roată–drum accelerează doar masa M, a = (μ·F_z − F_rez)/M; cuplul suplimentar pentru masele în rotație îl furnizează motorul. Cu δ = 1 cele două forme coincid.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculul regimurilor caracteristice – relațiile din cursul C1</t>
   </si>
   <si>
     <t xml:space="preserve">Fiecare coloană este un regim de funcționare. Rândurile urmează succesiunea din curs: rezistențe → forța de tracțiune necesară → cuplu și putere → verificarea aderenței și a acționării.</t>
@@ -744,9 +700,6 @@
     <t xml:space="preserve">Forța maximă transmisibilă prin aderență μ·F_z</t>
   </si>
   <si>
-    <t xml:space="preserve">μ·F_z (μ = 0,85)</t>
-  </si>
-  <si>
     <t xml:space="preserve">(36)</t>
   </si>
   <si>
@@ -762,7 +715,7 @@
     <t xml:space="preserve">Verificare aderență F_t ≤ μ·F_z</t>
   </si>
   <si>
-    <t xml:space="preserve">(40)</t>
+    <t xml:space="preserve">(6)/(30) → (40)</t>
   </si>
   <si>
     <t xml:space="preserve">Forța maximă a acționării F_t,drive</t>
@@ -780,7 +733,7 @@
     <t xml:space="preserve">min(F_t,drive ; μ·F_z)</t>
   </si>
   <si>
-    <t xml:space="preserve">Limitarea dominantă</t>
+    <t xml:space="preserve">Limita activă pentru F_t,max</t>
   </si>
   <si>
     <t xml:space="preserve">(43)</t>
@@ -813,18 +766,12 @@
     <t xml:space="preserve">D1</t>
   </si>
   <si>
-    <t xml:space="preserve">Accelerația maximă la pornire, limitată de aderență (μ = 0,85)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(μ − f)·g / δ</t>
+    <t xml:space="preserve">(μ − f)·g  (forța de aderență accelerează doar masa M)</t>
   </si>
   <si>
     <t xml:space="preserve">D2</t>
   </si>
   <si>
-    <t xml:space="preserve">Panta maximă urcată limitată de aderență (μ = 0,85), v ≈ 0</t>
-  </si>
-  <si>
     <t xml:space="preserve">tg α = μ − f  (din μ·cos α ≥ f·cos α + sin α)</t>
   </si>
   <si>
@@ -876,16 +823,13 @@
     <t xml:space="preserve">D8</t>
   </si>
   <si>
-    <t xml:space="preserve">Viteza la care puterea de vârf egalează aderența (μ = 1,20)</t>
-  </si>
-  <si>
     <t xml:space="preserve">v = η·P_vârf / (μ_perf·M·g)</t>
   </si>
   <si>
     <t xml:space="preserve">Caracteristica de tracțiune F(v), puterea P(v) și estimarea accelerării</t>
   </si>
   <si>
-    <t xml:space="preserve">Pas de 5 km/h. F_t,drive = min(T_m,max·i_g·η/r_w ; η·P/v). F_t,max = min(F_t,drive ; μ·M·g). a = (F_t,max − F_ra − F_f)/(δ·M); timpul se obține prin integrare numerică: Δt = Δv / a_mediu (metoda trapezelor). Curba „continuu” folosește T_m,max la viteze mici, deoarece cuplul continuu nu este publicat.</t>
+    <t xml:space="preserve">Pas de 5 km/h. F_t,drive = min(T_m,max·i_g·η/r_w ; η·P/v). F_rez = F_ra + F_f. a = min[(μ·M·g − F_rez)/M ; (F_t,drive − F_rez)/(δ·M)]; timpul se obține prin integrare numerică: Δt = 2·Δv/(a_i + a_i+1) (regula trapezelor aplicată ecuației dv/dt = a). Curba pentru puterea continuă folosește T_m,max la viteze mici, deoarece cuplul continuu nu este publicat. Coloanele V–X: sensibilitate cu puterea medie P_cal în locul puterii de vârf.</t>
   </si>
   <si>
     <t xml:space="preserve">v [m/s]</t>
@@ -900,43 +844,13 @@
     <t xml:space="preserve">F_rez orizontal [N]</t>
   </si>
   <si>
-    <t xml:space="preserve">F_rez rampă 10 % [N]</t>
-  </si>
-  <si>
     <t xml:space="preserve">F_t,drive vârf [N]</t>
   </si>
   <si>
     <t xml:space="preserve">F_t,drive continuu [N]</t>
   </si>
   <si>
-    <t xml:space="preserve">μ·M·g (μ=0,85) [N]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">μ·M·g (μ=1,20) [N]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F_t,max μ=0,85 [N]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F_t,max μ=1,20 [N]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a μ=0,85 [m/s²]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a μ=1,20 [m/s²]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">t μ=0,85 [s]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">t μ=1,20 [s]</t>
-  </si>
-  <si>
     <t xml:space="preserve">P_m orizontal [kW]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P_m rampă 10 % [kW]</t>
   </si>
   <si>
     <t xml:space="preserve">P_vârf [kW]</t>
@@ -3216,7 +3130,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>μ·M·g (μ=0,85) [N]</c:v>
+                  <c:v>μ·M·g (μ = 0,85) [N]</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3655,7 +3569,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>μ·M·g (μ=1,20) [N]</c:v>
+                  <c:v>μ·M·g (μ = 1,20) [N]</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4085,11 +3999,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="24243518"/>
-        <c:axId val="48408042"/>
+        <c:axId val="84361848"/>
+        <c:axId val="4833042"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="24243518"/>
+        <c:axId val="84361848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="300"/>
@@ -4167,12 +4081,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48408042"/>
+        <c:crossAx val="4833042"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="48408042"/>
+        <c:axId val="4833042"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="35000"/>
@@ -4250,7 +4164,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24243518"/>
+        <c:crossAx val="84361848"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -6102,11 +6016,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="86512673"/>
-        <c:axId val="66308036"/>
+        <c:axId val="88679461"/>
+        <c:axId val="63434638"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="86512673"/>
+        <c:axId val="88679461"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="300"/>
@@ -6184,12 +6098,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66308036"/>
+        <c:crossAx val="63434638"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="66308036"/>
+        <c:axId val="63434638"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="900"/>
@@ -6267,7 +6181,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86512673"/>
+        <c:crossAx val="88679461"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -6323,13 +6237,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>22</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>160920</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>32</xdr:col>
+      <xdr:col>35</xdr:col>
       <xdr:colOff>364680</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>178920</xdr:rowOff>
@@ -6340,7 +6254,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="15202080" y="762120"/>
+        <a:off x="17457480" y="762120"/>
         <a:ext cx="6479640" cy="3599640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -6353,13 +6267,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>22</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>160560</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>32</xdr:col>
+      <xdr:col>35</xdr:col>
       <xdr:colOff>364680</xdr:colOff>
       <xdr:row>43</xdr:row>
       <xdr:rowOff>140760</xdr:rowOff>
@@ -6370,7 +6284,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="15202080" y="5295960"/>
+        <a:off x="17457480" y="5295960"/>
         <a:ext cx="6479640" cy="3599640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -6564,7 +6478,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -6635,8 +6549,8 @@
         <v>7</v>
       </c>
       <c r="D7" s="7" t="str">
-        <f aca="false">FIXED(f_r,3)&amp;" / "&amp;FIXED(mu_us,2)</f>
-        <v>0.012 / 0.85</v>
+        <f aca="false">SUBSTITUTE(FIXED(f_r,3,TRUE()),".",",")&amp;" / "&amp;SUBSTITUTE(FIXED(mu_us,2,TRUE()),".",",")</f>
+        <v>0,012 / 0,85</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>8</v>
@@ -6683,8 +6597,8 @@
         <v>13</v>
       </c>
       <c r="D11" s="7" t="str">
-        <f aca="false">FIXED(T_max,0,TRUE())&amp;" N·m / "&amp;FIXED(P_vf,0,TRUE())&amp;" kW / "&amp;FIXED(P_cont,0,TRUE())&amp;" kW"</f>
-        <v>2000 N·m / 860 kW / 530 kW</v>
+        <f aca="false">SUBSTITUTE(SUBSTITUTE(FIXED(T_max,0),","," "),"."," ")&amp;" N·m / "&amp;SUBSTITUTE(SUBSTITUTE(FIXED(P_vf,0),","," "),"."," ")&amp;" kW / "&amp;SUBSTITUTE(SUBSTITUTE(FIXED(P_cont,0),","," "),"."," ")&amp;" kW"</f>
+        <v>2 000 N·m / 860 kW / 530 kW</v>
       </c>
       <c r="E11" s="4"/>
     </row>
@@ -6741,8 +6655,9 @@
       <c r="A15" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="11" t="s">
-        <v>30</v>
+      <c r="B15" s="11" t="str">
+        <f aca="false">'Calcul regimuri'!E5</f>
+        <v>Viteză maximă 300 km/h, drum orizontal</v>
       </c>
       <c r="C15" s="12" t="n">
         <f aca="false">'Calcul regimuri'!E6</f>
@@ -6790,15 +6705,16 @@
       </c>
       <c r="N15" s="16" t="str">
         <f aca="false">'Calcul regimuri'!E28</f>
-        <v>acționare</v>
+        <v>– (rezervă)</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>32</v>
+        <v>30</v>
+      </c>
+      <c r="B16" s="11" t="str">
+        <f aca="false">'Calcul regimuri'!F5</f>
+        <v>Accelerare 0–100 km/h în 2,4 s – la pornire (v = 0)</v>
       </c>
       <c r="C16" s="12" t="n">
         <f aca="false">'Calcul regimuri'!F6</f>
@@ -6851,10 +6767,11 @@
     </row>
     <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>34</v>
+        <v>31</v>
+      </c>
+      <c r="B17" s="11" t="str">
+        <f aca="false">'Calcul regimuri'!G5</f>
+        <v>Accelerare 0–100 km/h în 2,4 s – la 100 km/h</v>
       </c>
       <c r="C17" s="12" t="n">
         <f aca="false">'Calcul regimuri'!G6</f>
@@ -6907,10 +6824,11 @@
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>36</v>
+        <v>32</v>
+      </c>
+      <c r="B18" s="11" t="str">
+        <f aca="false">'Calcul regimuri'!H5</f>
+        <v>Rampă 10 % la 100 km/h, viteză constantă</v>
       </c>
       <c r="C18" s="12" t="n">
         <f aca="false">'Calcul regimuri'!H6</f>
@@ -6958,15 +6876,16 @@
       </c>
       <c r="N18" s="16" t="str">
         <f aca="false">'Calcul regimuri'!H28</f>
-        <v>aderență</v>
+        <v>– (rezervă)</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>38</v>
+        <v>33</v>
+      </c>
+      <c r="B19" s="11" t="str">
+        <f aca="false">'Calcul regimuri'!I5</f>
+        <v>Pornire pe panta maximă de 30 % (v ≈ 0, a = 0)</v>
       </c>
       <c r="C19" s="12" t="n">
         <f aca="false">'Calcul regimuri'!I6</f>
@@ -7014,28 +6933,28 @@
       </c>
       <c r="N19" s="16" t="str">
         <f aca="false">'Calcul regimuri'!I28</f>
-        <v>aderență</v>
+        <v>– (rezervă)</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
       <c r="D22" s="9" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
@@ -7047,8 +6966,9 @@
       <c r="N22" s="9"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="17" t="s">
-        <v>44</v>
+      <c r="A23" s="17" t="str">
+        <f aca="false">"Timp 0–100 km/h, μ = "&amp;SUBSTITUTE(FIXED(mu_us,2,TRUE()),".",",")&amp;" (asfalt uscat, tabelul cursului) [s]"</f>
+        <v>Timp 0–100 km/h, μ = 0,85 (asfalt uscat, tabelul cursului) [s]</v>
       </c>
       <c r="B23" s="17"/>
       <c r="C23" s="17"/>
@@ -7060,8 +6980,9 @@
         <f aca="false">t_acc</f>
         <v>2.4</v>
       </c>
-      <c r="F23" s="20" t="s">
-        <v>45</v>
+      <c r="F23" s="20" t="str">
+        <f aca="false">"aderența limitează accelerarea"</f>
+        <v>aderența limitează accelerarea</v>
       </c>
       <c r="G23" s="20"/>
       <c r="H23" s="20"/>
@@ -7073,8 +6994,9 @@
       <c r="N23" s="20"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="17" t="s">
-        <v>46</v>
+      <c r="A24" s="17" t="str">
+        <f aca="false">"Timp 0–100 km/h, μ = "&amp;SUBSTITUTE(FIXED(mu_perf,2,TRUE()),".",",")&amp;" (anvelope de performanță) [s]"</f>
+        <v>Timp 0–100 km/h, μ = 1,20 (anvelope de performanță) [s]</v>
       </c>
       <c r="B24" s="17"/>
       <c r="C24" s="17"/>
@@ -7086,8 +7008,9 @@
         <f aca="false">t_acc</f>
         <v>2.4</v>
       </c>
-      <c r="F24" s="20" t="s">
-        <v>47</v>
+      <c r="F24" s="20" t="str">
+        <f aca="false">"calibrare: μ_perf ≈ μ necesar = "&amp;SUBSTITUTE(FIXED('Calcul regimuri'!F24,2,TRUE()),".",",")&amp;", deci nu este o verificare independentă"</f>
+        <v>calibrare: μ_perf ≈ μ necesar = 1,19, deci nu este o verificare independentă</v>
       </c>
       <c r="G24" s="20"/>
       <c r="H24" s="20"/>
@@ -7099,8 +7022,9 @@
       <c r="N24" s="20"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="17" t="s">
-        <v>48</v>
+      <c r="A25" s="17" t="str">
+        <f aca="false">"Timp 0–200 km/h, μ = "&amp;SUBSTITUTE(FIXED(mu_perf,2,TRUE()),".",",")&amp;", P_vârf = "&amp;SUBSTITUTE(SUBSTITUTE(FIXED(P_vf,0),","," "),"."," ")&amp;" kW [s]"</f>
+        <v>Timp 0–200 km/h, μ = 1,20, P_vârf = 860 kW [s]</v>
       </c>
       <c r="B25" s="17"/>
       <c r="C25" s="17"/>
@@ -7112,8 +7036,9 @@
         <f aca="false">t_200</f>
         <v>6.8</v>
       </c>
-      <c r="F25" s="20" t="s">
-        <v>49</v>
+      <c r="F25" s="20" t="str">
+        <f aca="false">"model optimist: puterea de vârf este considerată disponibilă integral până la 200 km/h"</f>
+        <v>model optimist: puterea de vârf este considerată disponibilă integral până la 200 km/h</v>
       </c>
       <c r="G25" s="20"/>
       <c r="H25" s="20"/>
@@ -7125,21 +7050,23 @@
       <c r="N25" s="20"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="17" t="s">
-        <v>50</v>
+      <c r="A26" s="17" t="str">
+        <f aca="false">"Timp 0–100 km/h, μ = "&amp;SUBSTITUTE(FIXED(mu_perf,2,TRUE()),".",",")&amp;", P_cal = "&amp;SUBSTITUTE(SUBSTITUTE(FIXED(P_cal,0),","," "),"."," ")&amp;" kW [s]"</f>
+        <v>Timp 0–100 km/h, μ = 1,20, P_cal = 750 kW [s]</v>
       </c>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
       <c r="D26" s="18" t="n">
-        <f aca="false">'Calcul regimuri'!E37</f>
-        <v>8.22078</v>
+        <f aca="false">INDEX('Caracteristica tractiune'!X5:X65,MATCH(v_acc,'Caracteristica tractiune'!A5:A65,0))</f>
+        <v>2.41876725801517</v>
       </c>
       <c r="E26" s="19" t="n">
-        <f aca="false">a_med</f>
-        <v>11.5740740740741</v>
-      </c>
-      <c r="F26" s="20" t="s">
-        <v>51</v>
+        <f aca="false">t_acc</f>
+        <v>2.4</v>
+      </c>
+      <c r="F26" s="20" t="str">
+        <f aca="false">"practic neschimbat: până la ≈ 100 km/h accelerarea este limitată de aderență"</f>
+        <v>practic neschimbat: până la ≈ 100 km/h accelerarea este limitată de aderență</v>
       </c>
       <c r="G26" s="20"/>
       <c r="H26" s="20"/>
@@ -7151,20 +7078,23 @@
       <c r="N26" s="20"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="17" t="s">
-        <v>52</v>
+      <c r="A27" s="17" t="str">
+        <f aca="false">"Timp 0–200 km/h, μ = "&amp;SUBSTITUTE(FIXED(mu_perf,2,TRUE()),".",",")&amp;", P_cal = "&amp;SUBSTITUTE(SUBSTITUTE(FIXED(P_cal,0),","," "),"."," ")&amp;" kW [s]"</f>
+        <v>Timp 0–200 km/h, μ = 1,20, P_cal = 750 kW [s]</v>
       </c>
       <c r="B27" s="17"/>
       <c r="C27" s="17"/>
       <c r="D27" s="18" t="n">
-        <f aca="false">'Calcul regimuri'!F24</f>
-        <v>1.19182406463548</v>
-      </c>
-      <c r="E27" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" s="20" t="s">
-        <v>53</v>
+        <f aca="false">INDEX('Caracteristica tractiune'!X5:X65,MATCH(200,'Caracteristica tractiune'!A5:A65,0))</f>
+        <v>6.79614415277472</v>
+      </c>
+      <c r="E27" s="19" t="n">
+        <f aca="false">t_200</f>
+        <v>6.8</v>
+      </c>
+      <c r="F27" s="20" t="str">
+        <f aca="false">"P_cal = puterea medie disponibilă care reproduce timpul oficial"</f>
+        <v>P_cal = puterea medie disponibilă care reproduce timpul oficial</v>
       </c>
       <c r="G27" s="20"/>
       <c r="H27" s="20"/>
@@ -7176,21 +7106,23 @@
       <c r="N27" s="20"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="17" t="s">
-        <v>54</v>
+      <c r="A28" s="17" t="str">
+        <f aca="false">"Accelerația maximă la pornire, μ = "&amp;SUBSTITUTE(FIXED(mu_us,2,TRUE()),".",",")&amp;" [m/s²]"</f>
+        <v>Accelerația maximă la pornire, μ = 0,85 [m/s²]</v>
       </c>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
-      <c r="D28" s="21" t="n">
-        <f aca="false">'Calcul regimuri'!E41</f>
-        <v>405.502763569018</v>
-      </c>
-      <c r="E28" s="22" t="n">
-        <f aca="false">v_max</f>
-        <v>300</v>
-      </c>
-      <c r="F28" s="20" t="s">
-        <v>55</v>
+      <c r="D28" s="18" t="n">
+        <f aca="false">'Calcul regimuri'!E37</f>
+        <v>8.22078</v>
+      </c>
+      <c r="E28" s="19" t="n">
+        <f aca="false">a_med</f>
+        <v>11.5740740740741</v>
+      </c>
+      <c r="F28" s="20" t="str">
+        <f aca="false">"oficial = accelerația medie 0–100 km/h (din "&amp;SUBSTITUTE(FIXED(t_acc,1,TRUE()),".",",")&amp;" s)"</f>
+        <v>oficial = accelerația medie 0–100 km/h (din 2,4 s)</v>
       </c>
       <c r="G28" s="20"/>
       <c r="H28" s="20"/>
@@ -7202,20 +7134,22 @@
       <c r="N28" s="20"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="17" t="s">
-        <v>56</v>
+      <c r="A29" s="17" t="str">
+        <f aca="false">"Coeficient de aderență necesar pentru 0–100 km/h în "&amp;SUBSTITUTE(FIXED(t_acc,1,TRUE()),".",",")&amp;" s"</f>
+        <v>Coeficient de aderență necesar pentru 0–100 km/h în 2,4 s</v>
       </c>
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
-      <c r="D29" s="23" t="n">
-        <f aca="false">'Calcul regimuri'!E38</f>
-        <v>83.8</v>
-      </c>
-      <c r="E29" s="24" t="s">
+      <c r="D29" s="18" t="n">
+        <f aca="false">'Calcul regimuri'!F24</f>
+        <v>1.19182406463548</v>
+      </c>
+      <c r="E29" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="20" t="s">
-        <v>57</v>
+      <c r="F29" s="20" t="str">
+        <f aca="false">"regimul S2a"</f>
+        <v>regimul S2a</v>
       </c>
       <c r="G29" s="20"/>
       <c r="H29" s="20"/>
@@ -7228,20 +7162,21 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="17" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
-      <c r="D30" s="23" t="n">
-        <f aca="false">'Calcul regimuri'!E18</f>
-        <v>226.463516569201</v>
-      </c>
-      <c r="E30" s="24" t="n">
-        <f aca="false">P_cont</f>
-        <v>530</v>
-      </c>
-      <c r="F30" s="20" t="s">
-        <v>59</v>
+      <c r="D30" s="21" t="n">
+        <f aca="false">'Calcul regimuri'!E41</f>
+        <v>405.502763569018</v>
+      </c>
+      <c r="E30" s="22" t="n">
+        <f aca="false">v_max</f>
+        <v>300</v>
+      </c>
+      <c r="F30" s="20" t="str">
+        <f aca="false">"v_max = "&amp;SUBSTITUTE(SUBSTITUTE(FIXED(v_max,0),","," "),"."," ")&amp;" km/h este limitată electronic (oficial)"</f>
+        <v>v_max = 300 km/h este limitată electronic (oficial)</v>
       </c>
       <c r="G30" s="20"/>
       <c r="H30" s="20"/>
@@ -7252,53 +7187,70 @@
       <c r="M30" s="20"/>
       <c r="N30" s="20"/>
     </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="17" t="str">
+        <f aca="false">"Panta maximă, limită de aderență, μ = "&amp;SUBSTITUTE(FIXED(mu_us,2,TRUE()),".",",")&amp;" [%]"</f>
+        <v>Panta maximă, limită de aderență, μ = 0,85 [%]</v>
+      </c>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="23" t="n">
+        <f aca="false">'Calcul regimuri'!E38</f>
+        <v>83.8</v>
+      </c>
+      <c r="E31" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" s="20" t="str">
+        <f aca="false">"tracțiune integrală, distribuție ideală a cuplului"</f>
+        <v>tracțiune integrală, distribuție ideală a cuplului</v>
+      </c>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="20"/>
+      <c r="M31" s="20"/>
+      <c r="N31" s="20"/>
+    </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="25" t="str">
-        <f aca="false">"1. La v_max = "&amp;FIXED(v_max,0,TRUE())&amp;" km/h pe drum orizontal sunt necesari F_t = "&amp;FIXED('Calcul regimuri'!E15,0)&amp;" N la roți, adică P_m = "&amp;FIXED('Calcul regimuri'!E18,0,TRUE())&amp;" kW – doar "&amp;FIXED(100*('Calcul regimuri'!E31),0,TRUE())&amp;" %"&amp;" din puterea continuă; "&amp;FIXED(100*('Calcul regimuri'!E11/'Calcul regimuri'!E15),0,TRUE())&amp;" %"&amp;" din rezistență este aerodinamică. Viteza maximă nu este limitată de putere, ci electronic și de turația motoarelor ("&amp;FIXED('Calcul regimuri'!E21,0)&amp;" rot/min)."</f>
-        <v>1. La v_max = 300 km/h pe drum orizontal sunt necesari F_t = 2,582 N la roți, adică P_m = 226 kW – doar 43 % din puterea continuă; 88 % din rezistență este aerodinamică. Viteza maximă nu este limitată de putere, ci electronic și de turația motoarelor (13,000 rot/min).</v>
-      </c>
-      <c r="B33" s="25"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="25"/>
-      <c r="I33" s="25"/>
-      <c r="J33" s="25"/>
-      <c r="K33" s="25"/>
-      <c r="L33" s="25"/>
-      <c r="M33" s="25"/>
-      <c r="N33" s="25"/>
-    </row>
-    <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="25" t="str">
-        <f aca="false">"2. Accelerarea 0–100 km/h în "&amp;FIXED(t_acc,1)&amp;" s cere o forță de "&amp;FIXED('Calcul regimuri'!F15,0)&amp;" N la pornire, deci μ ≥ "&amp;FIXED('Calcul regimuri'!F24,2)&amp;". Cu μ = "&amp;FIXED(mu_us,2)&amp;" (asfalt uscat, tabelul cursului) forța transmisibilă este doar "&amp;FIXED('Calcul regimuri'!F23,0)&amp;" N, iar timpul minim estimat este "&amp;FIXED(D23,1)&amp;" s: performanța este limitată de aderență, nu de acționare (F_t,drive = "&amp;FIXED('Calcul regimuri'!F26,0)&amp;" N)."</f>
-        <v>2. Accelerarea 0–100 km/h în 2.4 s cere o forță de 29,639 N la pornire, deci μ ≥ 1.19. Cu μ = 0.85 (asfalt uscat, tabelul cursului) forța transmisibilă este doar 21,138 N, iar timpul minim estimat este 3.4 s: performanța este limitată de aderență, nu de acționare (F_t,drive = 31,039 N).</v>
-      </c>
-      <c r="B34" s="25"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
-      <c r="I34" s="25"/>
-      <c r="J34" s="25"/>
-      <c r="K34" s="25"/>
-      <c r="L34" s="25"/>
-      <c r="M34" s="25"/>
-      <c r="N34" s="25"/>
-    </row>
-    <row r="35" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="17" t="str">
+        <f aca="false">"Puterea motoarelor la v_max = "&amp;SUBSTITUTE(SUBSTITUTE(FIXED(v_max,0),","," "),"."," ")&amp;" km/h [kW]"</f>
+        <v>Puterea motoarelor la v_max = 300 km/h [kW]</v>
+      </c>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="23" t="n">
+        <f aca="false">'Calcul regimuri'!E18</f>
+        <v>226.463516569201</v>
+      </c>
+      <c r="E32" s="24" t="n">
+        <f aca="false">P_cont</f>
+        <v>530</v>
+      </c>
+      <c r="F32" s="20" t="str">
+        <f aca="false">"comparată cu puterea continuă"</f>
+        <v>comparată cu puterea continuă</v>
+      </c>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="20"/>
+      <c r="L32" s="20"/>
+      <c r="M32" s="20"/>
+      <c r="N32" s="20"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="25" t="str">
-        <f aca="false">"3. Cu anvelope de performanță (μ = "&amp;FIXED(mu_perf,2)&amp;") modelul dă 0–100 km/h în "&amp;FIXED(D24,2)&amp;" s (oficial "&amp;FIXED(t_acc,1)&amp;" s) și 0–200 km/h în "&amp;FIXED(D25,1)&amp;" s (oficial "&amp;FIXED(t_200,1)&amp;" s, abatere "&amp;FIXED(100*(ABS(D25/t_200-1)),0,TRUE())&amp;" %"&amp;"). Abaterea la 0–200 km/h provine în principal din neglijarea maselor în rotație (δ = 1, rel. 23) și a pierderilor din invertor și baterie; ipotezele pentru r_w, i_g și η sunt plauzibile."</f>
-        <v>3. Cu anvelope de performanță (μ = 1.20) modelul dă 0–100 km/h în 2.39 s (oficial 2.4 s) și 0–200 km/h în 6.2 s (oficial 6.8 s, abatere 9 %). Abaterea la 0–200 km/h provine în principal din neglijarea maselor în rotație (δ = 1, rel. 23) și a pierderilor din invertor și baterie; ipotezele pentru r_w, i_g și η sunt plauzibile.</v>
+        <f aca="false">"1. La v_max = "&amp;SUBSTITUTE(SUBSTITUTE(FIXED(v_max,0),","," "),"."," ")&amp;" km/h pe drum orizontal sunt necesari F_t = "&amp;SUBSTITUTE(SUBSTITUTE(FIXED('Calcul regimuri'!E15,0),","," "),"."," ")&amp;" N la roți, adică P_m = "&amp;SUBSTITUTE(SUBSTITUTE(FIXED('Calcul regimuri'!E18,0),","," "),"."," ")&amp;" kW – doar "&amp;FIXED(100*('Calcul regimuri'!E31),0,TRUE())&amp;" %"&amp;" din puterea continuă; "&amp;FIXED(100*('Calcul regimuri'!E11/'Calcul regimuri'!E15),0,TRUE())&amp;" %"&amp;" din rezistență este aerodinamică. Viteza maximă nu este limitată de putere (cu puterea continuă ar fi posibilă teoretic ≈ "&amp;SUBSTITUTE(SUBSTITUTE(FIXED('Calcul regimuri'!E41,0),","," "),"."," ")&amp;" km/h), ci electronic, conform datelor oficiale. Turația de "&amp;SUBSTITUTE(SUBSTITUTE(FIXED(n_m_vmax,0),","," "),"."," ")&amp;" rot/min la v_max este o dată de intrare (folosită pentru estimarea i_g), nu un rezultat al calculului."</f>
+        <v>1. La v_max = 300 km/h pe drum orizontal sunt necesari F_t = 2 582 N la roți, adică P_m = 226 kW – doar 43 % din puterea continuă; 88 % din rezistență este aerodinamică. Viteza maximă nu este limitată de putere (cu puterea continuă ar fi posibilă teoretic ≈ 406 km/h), ci electronic, conform datelor oficiale. Turația de 13 000 rot/min la v_max este o dată de intrare (folosită pentru estimarea i_g), nu un rezultat al calculului.</v>
       </c>
       <c r="B35" s="25"/>
       <c r="C35" s="25"/>
@@ -7314,10 +7266,10 @@
       <c r="M35" s="25"/>
       <c r="N35" s="25"/>
     </row>
-    <row r="36" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="25" t="str">
-        <f aca="false">"4. La 100 km/h, accelerația medie impusă ar cere P_m = "&amp;FIXED('Calcul regimuri'!G18,0,TRUE())&amp;" kW ("&amp;FIXED(100*('Calcul regimuri'!G32),0,TRUE())&amp;" %"&amp;" din puterea de vârf de "&amp;FIXED(P_vf,0,TRUE())&amp;" kW): accelerarea reală scade odată cu viteza, iar puterea de vârf este necesară doar pentru performanța maximă (Launch Control)."</f>
-        <v>4. La 100 km/h, accelerația medie impusă ar cere P_m = 874 kW (102 % din puterea de vârf de 860 kW): accelerarea reală scade odată cu viteza, iar puterea de vârf este necesară doar pentru performanța maximă (Launch Control).</v>
+        <f aca="false">"2. Accelerarea 0–"&amp;SUBSTITUTE(SUBSTITUTE(FIXED(v_acc,0),","," "),"."," ")&amp;" km/h în "&amp;SUBSTITUTE(FIXED(t_acc,1,TRUE()),".",",")&amp;" s cere o forță de "&amp;SUBSTITUTE(SUBSTITUTE(FIXED('Calcul regimuri'!F15,0),","," "),"."," ")&amp;" N la pornire, deci μ ≥ "&amp;SUBSTITUTE(FIXED('Calcul regimuri'!F24,2,TRUE()),".",",")&amp;". Cu μ = "&amp;SUBSTITUTE(FIXED(mu_us,2,TRUE()),".",",")&amp;" (asfalt uscat, tabelul cursului) se pot transmite doar "&amp;SUBSTITUTE(SUBSTITUTE(FIXED('Calcul regimuri'!F23,0),","," "),"."," ")&amp;" N din cei "&amp;SUBSTITUTE(SUBSTITUTE(FIXED('Calcul regimuri'!F26,0),","," "),"."," ")&amp;" N pe care îi poate furniza acționarea, iar timpul minim estimat este "&amp;SUBSTITUTE(FIXED(D23,1,TRUE()),".",",")&amp;" s: accelerarea este limitată de aderență, nu de acționare."</f>
+        <v>2. Accelerarea 0–100 km/h în 2,4 s cere o forță de 29 639 N la pornire, deci μ ≥ 1,19. Cu μ = 0,85 (asfalt uscat, tabelul cursului) se pot transmite doar 21 138 N din cei 31 039 N pe care îi poate furniza acționarea, iar timpul minim estimat este 3,4 s: accelerarea este limitată de aderență, nu de acționare.</v>
       </c>
       <c r="B36" s="25"/>
       <c r="C36" s="25"/>
@@ -7333,10 +7285,10 @@
       <c r="M36" s="25"/>
       <c r="N36" s="25"/>
     </row>
-    <row r="37" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="25" t="str">
-        <f aca="false">"5. Rampa de "&amp;FIXED(p_1,0,TRUE())&amp;" % la "&amp;FIXED(v_p1,0,TRUE())&amp;" km/h cere "&amp;FIXED('Calcul regimuri'!H18,0,TRUE())&amp;" kW, iar pornirea pe panta de "&amp;FIXED(p_max,0,TRUE())&amp;" % cere "&amp;FIXED('Calcul regimuri'!I15,0)&amp;" N (μ_nec = "&amp;FIXED('Calcul regimuri'!I24,2)&amp;"): ambele sunt îndeplinite cu rezervă mare."</f>
-        <v>5. Rampa de 10 % la 100 km/h cere 88 kW, iar pornirea pe panta de 30 % cere 7,432 N (μ_nec = 0.31): ambele sunt îndeplinite cu rezervă mare.</v>
+        <f aca="false">"3. Timpul oficial de "&amp;SUBSTITUTE(FIXED(t_acc,1,TRUE()),".",",")&amp;" s se obține numai cu μ ≈ "&amp;SUBSTITUTE(FIXED('Calcul regimuri'!F24,2,TRUE()),".",",")&amp;" (anvelope sport pe asfalt uscat, peste valorile din tabelul cursului); cu μ = "&amp;SUBSTITUTE(FIXED(mu_perf,2,TRUE()),".",",")&amp;" modelul dă "&amp;SUBSTITUTE(FIXED(D24,2,TRUE()),".",",")&amp;" s – aceasta este o calibrare a lui μ, nu o verificare independentă. Raza r_w și raportul i_g nu influențează forțele, puterile și timpii, deoarece i_g este calculat din r_w; ele afectează doar T_w și n_w."</f>
+        <v>3. Timpul oficial de 2,4 s se obține numai cu μ ≈ 1,19 (anvelope sport pe asfalt uscat, peste valorile din tabelul cursului); cu μ = 1,20 modelul dă 2,39 s – aceasta este o calibrare a lui μ, nu o verificare independentă. Raza r_w și raportul i_g nu influențează forțele, puterile și timpii, deoarece i_g este calculat din r_w; ele afectează doar T_w și n_w.</v>
       </c>
       <c r="B37" s="25"/>
       <c r="C37" s="25"/>
@@ -7352,10 +7304,10 @@
       <c r="M37" s="25"/>
       <c r="N37" s="25"/>
     </row>
-    <row r="38" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="25" t="str">
-        <f aca="false">"6. Date de confirmat în etapele următoare: dimensiunea anvelopelor (r_w), rapoartele reale de transmitere față/spate, distribuția cuplului între punți și cuplul continuu al motoarelor."</f>
-        <v>6. Date de confirmat în etapele următoare: dimensiunea anvelopelor (r_w), rapoartele reale de transmitere față/spate, distribuția cuplului între punți și cuplul continuu al motoarelor.</v>
+        <f aca="false">"4. Peste ≈ "&amp;SUBSTITUTE(SUBSTITUTE(FIXED('Calcul regimuri'!E44,0),","," "),"."," ")&amp;" km/h accelerarea este limitată de putere. Cu P_vârf = "&amp;SUBSTITUTE(SUBSTITUTE(FIXED(P_vf,0),","," "),"."," ")&amp;" kW (η·P = "&amp;SUBSTITUTE(SUBSTITUTE(FIXED(eta_t*P_vf,0),","," "),"."," ")&amp;" kW la roți) modelul dă 0–200 km/h în "&amp;SUBSTITUTE(FIXED(D25,2,TRUE()),".",",")&amp;" s, cu "&amp;FIXED(100*(1-D25/t_200),0,TRUE())&amp;" %"&amp;" mai repede decât valoarea oficială de "&amp;SUBSTITUTE(FIXED(t_200,1,TRUE()),".",",")&amp;" s; timpul oficial se obține cu o putere medie disponibilă de ≈ "&amp;SUBSTITUTE(SUBSTITUTE(FIXED(P_cal,0),","," "),"."," ")&amp;" kW ("&amp;SUBSTITUTE(FIXED(D27,2,TRUE()),".",",")&amp;" s). Cauze posibile: puterea de vârf nu este disponibilă integral pe tot intervalul 100–200 km/h, randamentul real scade la turații mari, iar masele în rotație au fost neglijate (δ = 1, rel. 23)."</f>
+        <v>4. Peste ≈ 99 km/h accelerarea este limitată de putere. Cu P_vârf = 860 kW (η·P = 817 kW la roți) modelul dă 0–200 km/h în 6,18 s, cu 9 % mai repede decât valoarea oficială de 6,8 s; timpul oficial se obține cu o putere medie disponibilă de ≈ 750 kW (6,80 s). Cauze posibile: puterea de vârf nu este disponibilă integral pe tot intervalul 100–200 km/h, randamentul real scade la turații mari, iar masele în rotație au fost neglijate (δ = 1, rel. 23).</v>
       </c>
       <c r="B38" s="25"/>
       <c r="C38" s="25"/>
@@ -7371,8 +7323,65 @@
       <c r="M38" s="25"/>
       <c r="N38" s="25"/>
     </row>
+    <row r="39" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="25" t="str">
+        <f aca="false">"5. La "&amp;SUBSTITUTE(SUBSTITUTE(FIXED(v_acc,0),","," "),"."," ")&amp;" km/h, accelerația medie impusă ("&amp;SUBSTITUTE(FIXED(a_med,2,TRUE()),".",",")&amp;" m/s²) ar cere P_m = "&amp;SUBSTITUTE(SUBSTITUTE(FIXED('Calcul regimuri'!G18,0),","," "),"."," ")&amp;" kW ("&amp;FIXED(100*('Calcul regimuri'!G32),0,TRUE())&amp;" %"&amp;" din puterea de vârf): accelerația reală scade odată cu viteza, iar puterea de vârf este necesară doar pentru performanța maximă (Launch Control)."</f>
+        <v>5. La 100 km/h, accelerația medie impusă (11,57 m/s²) ar cere P_m = 874 kW (102 % din puterea de vârf): accelerația reală scade odată cu viteza, iar puterea de vârf este necesară doar pentru performanța maximă (Launch Control).</v>
+      </c>
+      <c r="B39" s="25"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="25"/>
+      <c r="I39" s="25"/>
+      <c r="J39" s="25"/>
+      <c r="K39" s="25"/>
+      <c r="L39" s="25"/>
+      <c r="M39" s="25"/>
+      <c r="N39" s="25"/>
+    </row>
+    <row r="40" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="25" t="str">
+        <f aca="false">"6. Rampa de "&amp;SUBSTITUTE(SUBSTITUTE(FIXED(p_1,0),","," "),"."," ")&amp;" % la "&amp;SUBSTITUTE(SUBSTITUTE(FIXED(v_p1,0),","," "),"."," ")&amp;" km/h cere "&amp;SUBSTITUTE(SUBSTITUTE(FIXED('Calcul regimuri'!H18,0),","," "),"."," ")&amp;" kW, iar pornirea pe panta de "&amp;SUBSTITUTE(SUBSTITUTE(FIXED(p_max,0),","," "),"."," ")&amp;" % cere "&amp;SUBSTITUTE(SUBSTITUTE(FIXED('Calcul regimuri'!I15,0),","," "),"."," ")&amp;" N (μ necesar "&amp;SUBSTITUTE(FIXED('Calcul regimuri'!I24,2,TRUE()),".",",")&amp;"): ambele condiții sunt îndeplinite cu rezervă mare."</f>
+        <v>6. Rampa de 10 % la 100 km/h cere 88 kW, iar pornirea pe panta de 30 % cere 7 432 N (μ necesar 0,31): ambele condiții sunt îndeplinite cu rezervă mare.</v>
+      </c>
+      <c r="B40" s="25"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="25"/>
+      <c r="H40" s="25"/>
+      <c r="I40" s="25"/>
+      <c r="J40" s="25"/>
+      <c r="K40" s="25"/>
+      <c r="L40" s="25"/>
+      <c r="M40" s="25"/>
+      <c r="N40" s="25"/>
+    </row>
+    <row r="41" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="25" t="str">
+        <f aca="false">"7. Date de confirmat în etapele următoare: dimensiunea anvelopelor (r_w), rapoartele reale de transmitere față/spate, distribuția cuplului între punți (cap. 10, rel. 39), cuplul continuu al motoarelor și curba reală a puterii de vârf în funcție de viteză."</f>
+        <v>7. Date de confirmat în etapele următoare: dimensiunea anvelopelor (r_w), rapoartele reale de transmitere față/spate, distribuția cuplului între punți (cap. 10, rel. 39), cuplul continuu al motoarelor și curba reală a puterii de vârf în funcție de viteză.</v>
+      </c>
+      <c r="B41" s="25"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="25"/>
+      <c r="H41" s="25"/>
+      <c r="I41" s="25"/>
+      <c r="J41" s="25"/>
+      <c r="K41" s="25"/>
+      <c r="L41" s="25"/>
+      <c r="M41" s="25"/>
+      <c r="N41" s="25"/>
+    </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="30">
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="F22:N22"/>
@@ -7392,12 +7401,17 @@
     <mergeCell ref="F29:N29"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="F30:N30"/>
-    <mergeCell ref="A33:N33"/>
-    <mergeCell ref="A34:N34"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="F31:N31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="F32:N32"/>
     <mergeCell ref="A35:N35"/>
     <mergeCell ref="A36:N36"/>
     <mergeCell ref="A37:N37"/>
     <mergeCell ref="A38:N38"/>
+    <mergeCell ref="A39:N39"/>
+    <mergeCell ref="A40:N40"/>
+    <mergeCell ref="A41:N41"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7414,7 +7428,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
@@ -7427,12 +7441,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="26" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -7442,27 +7456,27 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="B5" s="28"/>
       <c r="C5" s="28"/>
@@ -7472,10 +7486,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="29" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="C6" s="30" t="n">
         <v>2460</v>
@@ -7484,18 +7498,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="29" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="C7" s="32" t="n">
         <v>75</v>
@@ -7504,18 +7518,18 @@
         <v>4</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="29" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="C8" s="14" t="n">
         <f aca="false">M_DIN+m_sofer</f>
@@ -7525,18 +7539,18 @@
         <v>4</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="29" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="C9" s="33" t="n">
         <v>0.22</v>
@@ -7545,18 +7559,18 @@
         <v>8</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="29" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="C10" s="33" t="n">
         <v>2.44</v>
@@ -7565,135 +7579,135 @@
         <v>6</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="29" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="C11" s="30" t="n">
         <v>2000</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="29" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="C12" s="30" t="n">
         <v>860</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="29" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="C13" s="30" t="n">
         <v>530</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="29" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="C14" s="32" t="n">
         <v>300</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="29" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C15" s="34" t="n">
         <v>2.4</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="29" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="C16" s="34" t="n">
         <v>6.8</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="B17" s="28"/>
       <c r="C17" s="28"/>
@@ -7703,50 +7717,50 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="29" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="C18" s="32" t="n">
         <v>21</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="F18" s="31" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="29" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C19" s="32" t="n">
         <v>295</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="29" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="C20" s="33" t="n">
         <v>0.3</v>
@@ -7755,18 +7769,18 @@
         <v>8</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="F20" s="31" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="29" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C21" s="33" t="n">
         <v>0.97</v>
@@ -7775,15 +7789,15 @@
         <v>8</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="F21" s="31" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="29" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="B22" s="17" t="s">
         <v>9</v>
@@ -7796,38 +7810,38 @@
         <v>10</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F22" s="31" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="29" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="C23" s="30" t="n">
         <v>13000</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="F23" s="31" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="29" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="C24" s="13" t="n">
         <f aca="false">n_m_vmax/(v_max/3.6/(2*PI()*r_w)*60)</f>
@@ -7837,18 +7851,18 @@
         <v>8</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F24" s="31" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="29" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="C25" s="33" t="n">
         <v>0.95</v>
@@ -7857,18 +7871,18 @@
         <v>8</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="F25" s="31" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="29" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="C26" s="33" t="n">
         <v>1</v>
@@ -7877,15 +7891,15 @@
         <v>8</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="F26" s="31" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="B27" s="28"/>
       <c r="C27" s="28"/>
@@ -7895,19 +7909,19 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="29" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C28" s="33" t="n">
         <v>9.81</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="F28" s="31" t="s">
         <v>8</v>
@@ -7915,30 +7929,30 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="29" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="C29" s="36" t="n">
         <v>1.225</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="F29" s="31" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="29" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="C30" s="36" t="n">
         <v>0.012</v>
@@ -7947,18 +7961,18 @@
         <v>8</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="F30" s="31" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="29" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="C31" s="33" t="n">
         <v>0.85</v>
@@ -7967,18 +7981,18 @@
         <v>8</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="F31" s="31" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="29" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="C32" s="33" t="n">
         <v>1.2</v>
@@ -7987,146 +8001,171 @@
         <v>8</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>76</v>
+        <v>135</v>
       </c>
       <c r="F32" s="31" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="27" t="s">
-        <v>156</v>
-      </c>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="C33" s="30" t="n">
+        <v>750</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="F33" s="31" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="29" t="s">
-        <v>157</v>
-      </c>
-      <c r="B34" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="C34" s="32" t="n">
-        <v>100</v>
-      </c>
-      <c r="D34" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="E34" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="F34" s="31" t="s">
-        <v>159</v>
-      </c>
+      <c r="A34" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="B34" s="28"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="29" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="C35" s="13" t="n">
+        <v>142</v>
+      </c>
+      <c r="C35" s="32" t="n">
+        <v>100</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F35" s="31" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="B36" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="C36" s="13" t="n">
         <f aca="false">v_acc/3.6/t_acc</f>
         <v>11.5740740740741</v>
       </c>
-      <c r="D35" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="E35" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="F35" s="31" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="B36" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="C36" s="32" t="n">
-        <v>10</v>
-      </c>
       <c r="D36" s="17" t="s">
-        <v>165</v>
+        <v>121</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>136</v>
+        <v>60</v>
       </c>
       <c r="F36" s="31" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="29" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="C37" s="32" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>99</v>
+        <v>149</v>
       </c>
       <c r="E37" s="17" t="s">
-        <v>76</v>
+        <v>116</v>
       </c>
       <c r="F37" s="31" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="29" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="C38" s="32" t="n">
+        <v>100</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="F38" s="31" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="C39" s="32" t="n">
         <v>30</v>
       </c>
-      <c r="D38" s="17" t="s">
-        <v>165</v>
-      </c>
-      <c r="E38" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="F38" s="31" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="37" t="s">
-        <v>173</v>
+      <c r="D39" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="F39" s="31" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="s">
-        <v>174</v>
+      <c r="A41" s="37" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>177</v>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="4" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -8160,12 +8199,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -8178,63 +8217,68 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>29</v>
       </c>
       <c r="F4" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="H4" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="9" t="s">
         <v>33</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5" s="38" t="s">
-        <v>38</v>
+      <c r="E5" s="38" t="str">
+        <f aca="false">"Viteză maximă "&amp;SUBSTITUTE(SUBSTITUTE(FIXED(v_max,0),","," "),"."," ")&amp;" km/h, drum orizontal"</f>
+        <v>Viteză maximă 300 km/h, drum orizontal</v>
+      </c>
+      <c r="F5" s="38" t="str">
+        <f aca="false">"Accelerare 0–"&amp;SUBSTITUTE(SUBSTITUTE(FIXED(v_acc,0),","," "),"."," ")&amp;" km/h în "&amp;SUBSTITUTE(FIXED(t_acc,1,TRUE()),".",",")&amp;" s – la pornire (v = 0)"</f>
+        <v>Accelerare 0–100 km/h în 2,4 s – la pornire (v = 0)</v>
+      </c>
+      <c r="G5" s="38" t="str">
+        <f aca="false">"Accelerare 0–"&amp;SUBSTITUTE(SUBSTITUTE(FIXED(v_acc,0),","," "),"."," ")&amp;" km/h în "&amp;SUBSTITUTE(FIXED(t_acc,1,TRUE()),".",",")&amp;" s – la "&amp;SUBSTITUTE(SUBSTITUTE(FIXED(v_acc,0),","," "),"."," ")&amp;" km/h"</f>
+        <v>Accelerare 0–100 km/h în 2,4 s – la 100 km/h</v>
+      </c>
+      <c r="H5" s="38" t="str">
+        <f aca="false">"Rampă "&amp;SUBSTITUTE(SUBSTITUTE(FIXED(p_1,0),","," "),"."," ")&amp;" % la "&amp;SUBSTITUTE(SUBSTITUTE(FIXED(v_p1,0),","," "),"."," ")&amp;" km/h, viteză constantă"</f>
+        <v>Rampă 10 % la 100 km/h, viteză constantă</v>
+      </c>
+      <c r="I5" s="38" t="str">
+        <f aca="false">"Pornire pe panta maximă de "&amp;SUBSTITUTE(SUBSTITUTE(FIXED(p_max,0),","," "),"."," ")&amp;" % (v ≈ 0, a = 0)"</f>
+        <v>Pornire pe panta maximă de 30 % (v ≈ 0, a = 0)</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="17"/>
       <c r="B6" s="17" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="E6" s="12" t="n">
         <f aca="false">v_max</f>
@@ -8258,13 +8302,13 @@
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="17"/>
       <c r="B7" s="17" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="E7" s="13" t="n">
         <f aca="false">E6/3.6</f>
@@ -8290,13 +8334,13 @@
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="17"/>
       <c r="B8" s="17" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="E8" s="32" t="n">
         <v>0</v>
@@ -8318,16 +8362,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="E9" s="13" t="n">
         <f aca="false">DEGREES(ATAN(E8/100))</f>
@@ -8353,13 +8397,13 @@
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="17"/>
       <c r="B10" s="17" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="E10" s="33" t="n">
         <v>0</v>
@@ -8381,16 +8425,16 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="E11" s="14" t="n">
         <f aca="false">0.5*rho_aer*C_x*A_f*E7^2</f>
@@ -8415,16 +8459,16 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="E12" s="14" t="n">
         <f aca="false">f_r*M_calc*g_acc*COS(RADIANS(E9))</f>
@@ -8449,16 +8493,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="E13" s="14" t="n">
         <f aca="false">M_calc*g_acc*SIN(RADIANS(E9))</f>
@@ -8483,16 +8527,16 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="E14" s="14" t="n">
         <f aca="false">delta_m*M_calc*E10</f>
@@ -8517,16 +8561,16 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="E15" s="39" t="n">
         <f aca="false">SUM(E11:E14)</f>
@@ -8551,16 +8595,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="B16" s="29" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="E16" s="39" t="n">
         <f aca="false">E15*r_w</f>
@@ -8585,16 +8629,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="B17" s="29" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="E17" s="40" t="n">
         <f aca="false">E15*E7/1000</f>
@@ -8619,16 +8663,16 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="B18" s="29" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="E18" s="40" t="n">
         <f aca="false">E17/eta_t</f>
@@ -8653,16 +8697,16 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="17" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="B19" s="29" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="E19" s="39" t="n">
         <f aca="false">E15*r_w/(i_g*eta_t)</f>
@@ -8688,13 +8732,13 @@
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="17"/>
       <c r="B20" s="17" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="E20" s="14" t="n">
         <f aca="false">E7/(2*PI()*r_w)*60</f>
@@ -8720,13 +8764,13 @@
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="17"/>
       <c r="B21" s="29" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="E21" s="39" t="n">
         <f aca="false">E20*i_g</f>
@@ -8751,16 +8795,16 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="E22" s="14" t="n">
         <f aca="false">M_calc*g_acc*COS(RADIANS(E9))</f>
@@ -8785,16 +8829,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>228</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>229</v>
+        <v>213</v>
+      </c>
+      <c r="C23" s="17" t="str">
+        <f aca="false">"μ·F_z (μ = "&amp;SUBSTITUTE(FIXED(mu_us,2,TRUE()),".",",")&amp;")"</f>
+        <v>μ·F_z (μ = 0,85)</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="E23" s="14" t="n">
         <f aca="false">mu_us*E22</f>
@@ -8819,13 +8864,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="17" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="B24" s="29" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="D24" s="17" t="s">
         <v>8</v>
@@ -8853,10 +8898,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="17" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="B25" s="29" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="C25" s="17"/>
       <c r="D25" s="17"/>
@@ -8883,16 +8928,16 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="17" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="E26" s="14" t="n">
         <f aca="false">IF(E7=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_vf*1000/E7))</f>
@@ -8917,16 +8962,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="17" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="E27" s="14" t="n">
         <f aca="false">MIN(E26,E23)</f>
@@ -8952,37 +8997,37 @@
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="17"/>
       <c r="B28" s="17" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
       <c r="E28" s="16" t="str">
-        <f aca="false">IF(E26&lt;=E23,"acționare","aderență")</f>
-        <v>acționare</v>
+        <f aca="false">IF(E27&gt;=E15,"– (rezervă)",IF(E26&lt;=E23,"acționare","aderență"))</f>
+        <v>– (rezervă)</v>
       </c>
       <c r="F28" s="16" t="str">
-        <f aca="false">IF(F26&lt;=F23,"acționare","aderență")</f>
+        <f aca="false">IF(F27&gt;=F15,"– (rezervă)",IF(F26&lt;=F23,"acționare","aderență"))</f>
         <v>aderență</v>
       </c>
       <c r="G28" s="16" t="str">
-        <f aca="false">IF(G26&lt;=G23,"acționare","aderență")</f>
+        <f aca="false">IF(G27&gt;=G15,"– (rezervă)",IF(G26&lt;=G23,"acționare","aderență"))</f>
         <v>aderență</v>
       </c>
       <c r="H28" s="16" t="str">
-        <f aca="false">IF(H26&lt;=H23,"acționare","aderență")</f>
-        <v>aderență</v>
+        <f aca="false">IF(H27&gt;=H15,"– (rezervă)",IF(H26&lt;=H23,"acționare","aderență"))</f>
+        <v>– (rezervă)</v>
       </c>
       <c r="I28" s="16" t="str">
-        <f aca="false">IF(I26&lt;=I23,"acționare","aderență")</f>
-        <v>aderență</v>
+        <f aca="false">IF(I27&gt;=I15,"– (rezervă)",IF(I26&lt;=I23,"acționare","aderență"))</f>
+        <v>– (rezervă)</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="17" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="B29" s="29" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
@@ -9010,11 +9055,11 @@
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="17"/>
       <c r="B30" s="17" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="E30" s="43" t="n">
         <f aca="false">E27-E15</f>
@@ -9040,13 +9085,13 @@
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="17"/>
       <c r="B31" s="17" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="E31" s="44" t="n">
         <f aca="false">E18/P_cont</f>
@@ -9072,13 +9117,13 @@
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="17"/>
       <c r="B32" s="17" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="E32" s="44" t="n">
         <f aca="false">E18/P_vf</f>
@@ -9103,56 +9148,58 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="9" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="45" t="s">
-        <v>251</v>
-      </c>
-      <c r="B37" s="31" t="s">
-        <v>252</v>
+        <v>235</v>
+      </c>
+      <c r="B37" s="31" t="str">
+        <f aca="false">"Accelerația maximă la pornire, limitată de aderență (μ = "&amp;SUBSTITUTE(FIXED(mu_us,2,TRUE()),".",",")&amp;")"</f>
+        <v>Accelerația maximă la pornire, limitată de aderență (μ = 0,85)</v>
       </c>
       <c r="C37" s="31" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="D37" s="45" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="E37" s="46" t="n">
-        <f aca="false">(mu_us-f_r)*g_acc/delta_m</f>
+        <f aca="false">(mu_us-f_r)*g_acc</f>
         <v>8.22078</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="45" t="s">
-        <v>254</v>
-      </c>
-      <c r="B38" s="31" t="s">
-        <v>255</v>
+        <v>237</v>
+      </c>
+      <c r="B38" s="31" t="str">
+        <f aca="false">"Panta maximă urcată, limitată de aderență (μ = "&amp;SUBSTITUTE(FIXED(mu_us,2,TRUE()),".",",")&amp;"), v ≈ 0"</f>
+        <v>Panta maximă urcată, limitată de aderență (μ = 0,85), v ≈ 0</v>
       </c>
       <c r="C38" s="31" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="D38" s="45" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="E38" s="47" t="n">
         <f aca="false">(mu_us-f_r)*100</f>
@@ -9161,13 +9208,13 @@
     </row>
     <row r="39" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="45" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="B39" s="31" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="C39" s="31" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="D39" s="45" t="s">
         <v>8</v>
@@ -9179,16 +9226,16 @@
     </row>
     <row r="40" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="45" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="B40" s="31" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="C40" s="31" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="D40" s="45" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="E40" s="47" t="str">
         <f aca="false">IF(E39&gt;SQRT(1+f_r^2),"nelimitată",100*TAN(ASIN(E39/SQRT(1+f_r^2))-ATAN(f_r)))</f>
@@ -9197,16 +9244,16 @@
     </row>
     <row r="41" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="45" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="B41" s="31" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="C41" s="31" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="D41" s="45" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="E41" s="48" t="n">
         <f aca="false">3.6*(POWER((eta_t*P_cont*1000/(0.5*rho_aer*C_x*A_f))/2+SQRT(((eta_t*P_cont*1000/(0.5*rho_aer*C_x*A_f)))^2/4+((f_r*M_calc*g_acc/(0.5*rho_aer*C_x*A_f)))^3/27),1/3)-POWER(SQRT(((eta_t*P_cont*1000/(0.5*rho_aer*C_x*A_f)))^2/4+((f_r*M_calc*g_acc/(0.5*rho_aer*C_x*A_f)))^3/27)-(eta_t*P_cont*1000/(0.5*rho_aer*C_x*A_f))/2,1/3))</f>
@@ -9215,16 +9262,16 @@
     </row>
     <row r="42" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="45" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="B42" s="31" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="C42" s="31" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="D42" s="45" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="E42" s="48" t="n">
         <f aca="false">3.6*(POWER((eta_t*P_vf*1000/(0.5*rho_aer*C_x*A_f))/2+SQRT(((eta_t*P_vf*1000/(0.5*rho_aer*C_x*A_f)))^2/4+((f_r*M_calc*g_acc/(0.5*rho_aer*C_x*A_f)))^3/27),1/3)-POWER(SQRT(((eta_t*P_vf*1000/(0.5*rho_aer*C_x*A_f)))^2/4+((f_r*M_calc*g_acc/(0.5*rho_aer*C_x*A_f)))^3/27)-(eta_t*P_vf*1000/(0.5*rho_aer*C_x*A_f))/2,1/3))</f>
@@ -9233,16 +9280,16 @@
     </row>
     <row r="43" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="45" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="B43" s="31" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="C43" s="31" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="D43" s="45" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="E43" s="47" t="n">
         <f aca="false">3.6*eta_t*P_vf*1000/(T_max*i_g*eta_t/r_w)</f>
@@ -9251,16 +9298,17 @@
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="45" t="s">
-        <v>272</v>
-      </c>
-      <c r="B44" s="31" t="s">
-        <v>273</v>
+        <v>254</v>
+      </c>
+      <c r="B44" s="31" t="str">
+        <f aca="false">"Viteza la care forța limitată de puterea de vârf egalează limita de aderență (μ = "&amp;SUBSTITUTE(FIXED(mu_perf,2,TRUE()),".",",")&amp;")"</f>
+        <v>Viteza la care forța limitată de puterea de vârf egalează limita de aderență (μ = 1,20)</v>
       </c>
       <c r="C44" s="31" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
       <c r="D44" s="45" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="E44" s="47" t="n">
         <f aca="false">3.6*eta_t*P_vf*1000/(mu_perf*M_calc*g_acc)</f>
@@ -9286,7 +9334,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:U65"/>
+  <dimension ref="A1:X65"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="8"/>
@@ -9297,16 +9345,18 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="17" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="19" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="23" style="0" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="26" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -9327,70 +9377,96 @@
       <c r="R2" s="26"/>
       <c r="S2" s="26"/>
       <c r="T2" s="26"/>
+      <c r="U2" s="26"/>
+      <c r="V2" s="26"/>
+      <c r="W2" s="26"/>
+      <c r="X2" s="26"/>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>281</v>
+        <v>261</v>
+      </c>
+      <c r="F4" s="9" t="str">
+        <f aca="false">"F_rez rampă "&amp;SUBSTITUTE(SUBSTITUTE(FIXED(p_1,0),","," "),"."," ")&amp;" % [N]"</f>
+        <v>F_rez rampă 10 % [N]</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>286</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>287</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="N4" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="O4" s="9" t="s">
-        <v>290</v>
-      </c>
-      <c r="P4" s="9" t="s">
-        <v>291</v>
+        <v>263</v>
+      </c>
+      <c r="I4" s="9" t="str">
+        <f aca="false">"μ·M·g (μ = "&amp;SUBSTITUTE(FIXED(mu_us,2,TRUE()),".",",")&amp;") [N]"</f>
+        <v>μ·M·g (μ = 0,85) [N]</v>
+      </c>
+      <c r="J4" s="9" t="str">
+        <f aca="false">"μ·M·g (μ = "&amp;SUBSTITUTE(FIXED(mu_perf,2,TRUE()),".",",")&amp;") [N]"</f>
+        <v>μ·M·g (μ = 1,20) [N]</v>
+      </c>
+      <c r="K4" s="9" t="str">
+        <f aca="false">"F_t,max μ = "&amp;SUBSTITUTE(FIXED(mu_us,2,TRUE()),".",",")&amp;" [N]"</f>
+        <v>F_t,max μ = 0,85 [N]</v>
+      </c>
+      <c r="L4" s="9" t="str">
+        <f aca="false">"F_t,max μ = "&amp;SUBSTITUTE(FIXED(mu_perf,2,TRUE()),".",",")&amp;" [N]"</f>
+        <v>F_t,max μ = 1,20 [N]</v>
+      </c>
+      <c r="M4" s="9" t="str">
+        <f aca="false">"a μ = "&amp;SUBSTITUTE(FIXED(mu_us,2,TRUE()),".",",")&amp;" [m/s²]"</f>
+        <v>a μ = 0,85 [m/s²]</v>
+      </c>
+      <c r="N4" s="9" t="str">
+        <f aca="false">"a μ = "&amp;SUBSTITUTE(FIXED(mu_perf,2,TRUE()),".",",")&amp;" [m/s²]"</f>
+        <v>a μ = 1,20 [m/s²]</v>
+      </c>
+      <c r="O4" s="9" t="str">
+        <f aca="false">"t μ = "&amp;SUBSTITUTE(FIXED(mu_us,2,TRUE()),".",",")&amp;" [s]"</f>
+        <v>t μ = 0,85 [s]</v>
+      </c>
+      <c r="P4" s="9" t="str">
+        <f aca="false">"t μ = "&amp;SUBSTITUTE(FIXED(mu_perf,2,TRUE()),".",",")&amp;" [s]"</f>
+        <v>t μ = 1,20 [s]</v>
       </c>
       <c r="Q4" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="R4" s="9" t="s">
-        <v>293</v>
+        <v>264</v>
+      </c>
+      <c r="R4" s="9" t="str">
+        <f aca="false">"P_m rampă "&amp;SUBSTITUTE(SUBSTITUTE(FIXED(p_1,0),","," "),"."," ")&amp;" % [kW]"</f>
+        <v>P_m rampă 10 % [kW]</v>
       </c>
       <c r="S4" s="9" t="s">
-        <v>294</v>
+        <v>265</v>
       </c>
       <c r="T4" s="9" t="s">
-        <v>295</v>
+        <v>266</v>
       </c>
       <c r="U4" s="9" t="s">
         <v>25</v>
+      </c>
+      <c r="V4" s="9" t="str">
+        <f aca="false">"F_t,drive P_cal = "&amp;SUBSTITUTE(SUBSTITUTE(FIXED(P_cal,0),","," "),"."," ")&amp;" kW [N]"</f>
+        <v>F_t,drive P_cal = 750 kW [N]</v>
+      </c>
+      <c r="W4" s="9" t="str">
+        <f aca="false">"a μ = "&amp;SUBSTITUTE(FIXED(mu_perf,2,TRUE()),".",",")&amp;", P_cal [m/s²]"</f>
+        <v>a μ = 1,20, P_cal [m/s²]</v>
+      </c>
+      <c r="X4" s="9" t="str">
+        <f aca="false">"t μ = "&amp;SUBSTITUTE(FIXED(mu_perf,2,TRUE()),".",",")&amp;", P_cal [s]"</f>
+        <v>t μ = 1,20, P_cal [s]</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9442,11 +9518,11 @@
         <v>29842.02</v>
       </c>
       <c r="M5" s="19" t="n">
-        <f aca="false">(K5-E5)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I5-E5)/M_calc,(G5-E5)/(delta_m*M_calc))</f>
         <v>8.22078</v>
       </c>
       <c r="N5" s="19" t="n">
-        <f aca="false">(L5-E5)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J5-E5)/M_calc,(G5-E5)/(delta_m*M_calc))</f>
         <v>11.65428</v>
       </c>
       <c r="O5" s="19" t="n">
@@ -9475,6 +9551,17 @@
         <f aca="false">B5/(2*PI()*r_w)*60*i_g</f>
         <v>0</v>
       </c>
+      <c r="V5" s="50" t="n">
+        <f aca="false">IF(B5=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B5))</f>
+        <v>31038.9354174672</v>
+      </c>
+      <c r="W5" s="19" t="n">
+        <f aca="false">MIN((J5-E5)/M_calc,(V5-E5)/(delta_m*M_calc))</f>
+        <v>11.65428</v>
+      </c>
+      <c r="X5" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="49" t="n">
@@ -9525,11 +9612,11 @@
         <v>29842.02</v>
       </c>
       <c r="M6" s="19" t="n">
-        <f aca="false">(K6-E6)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I6-E6)/M_calc,(G6-E6)/(delta_m*M_calc))</f>
         <v>8.22052980671829</v>
       </c>
       <c r="N6" s="19" t="n">
-        <f aca="false">(L6-E6)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J6-E6)/M_calc,(G6-E6)/(delta_m*M_calc))</f>
         <v>11.6540298067183</v>
       </c>
       <c r="O6" s="19" t="n">
@@ -9560,6 +9647,18 @@
         <f aca="false">B6/(2*PI()*r_w)*60*i_g</f>
         <v>216.666666666667</v>
       </c>
+      <c r="V6" s="50" t="n">
+        <f aca="false">IF(B6=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B6))</f>
+        <v>31038.9354174672</v>
+      </c>
+      <c r="W6" s="19" t="n">
+        <f aca="false">MIN((J6-E6)/M_calc,(V6-E6)/(delta_m*M_calc))</f>
+        <v>11.6540298067183</v>
+      </c>
+      <c r="X6" s="19" t="n">
+        <f aca="false">X5+(B6-B5)/((W6+W5)/2)</f>
+        <v>0.119175427167916</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="49" t="n">
@@ -9610,11 +9709,11 @@
         <v>29842.02</v>
       </c>
       <c r="M7" s="19" t="n">
-        <f aca="false">(K7-E7)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I7-E7)/M_calc,(G7-E7)/(delta_m*M_calc))</f>
         <v>8.21977922687316</v>
       </c>
       <c r="N7" s="19" t="n">
-        <f aca="false">(L7-E7)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J7-E7)/M_calc,(G7-E7)/(delta_m*M_calc))</f>
         <v>11.6532792268732</v>
       </c>
       <c r="O7" s="19" t="n">
@@ -9645,6 +9744,18 @@
         <f aca="false">B7/(2*PI()*r_w)*60*i_g</f>
         <v>433.333333333333</v>
       </c>
+      <c r="V7" s="50" t="n">
+        <f aca="false">IF(B7=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B7))</f>
+        <v>31038.9354174672</v>
+      </c>
+      <c r="W7" s="19" t="n">
+        <f aca="false">MIN((J7-E7)/M_calc,(V7-E7)/(delta_m*M_calc))</f>
+        <v>11.6532792268732</v>
+      </c>
+      <c r="X7" s="19" t="n">
+        <f aca="false">X6+(B7-B6)/((W7+W6)/2)</f>
+        <v>0.238355971510222</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="49" t="n">
@@ -9695,11 +9806,11 @@
         <v>29842.02</v>
       </c>
       <c r="M8" s="19" t="n">
-        <f aca="false">(K8-E8)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I8-E8)/M_calc,(G8-E8)/(delta_m*M_calc))</f>
         <v>8.21852826046461</v>
       </c>
       <c r="N8" s="19" t="n">
-        <f aca="false">(L8-E8)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J8-E8)/M_calc,(G8-E8)/(delta_m*M_calc))</f>
         <v>11.6520282604646</v>
       </c>
       <c r="O8" s="19" t="n">
@@ -9730,6 +9841,18 @@
         <f aca="false">B8/(2*PI()*r_w)*60*i_g</f>
         <v>650</v>
       </c>
+      <c r="V8" s="50" t="n">
+        <f aca="false">IF(B8=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B8))</f>
+        <v>31038.9354174672</v>
+      </c>
+      <c r="W8" s="19" t="n">
+        <f aca="false">MIN((J8-E8)/M_calc,(V8-E8)/(delta_m*M_calc))</f>
+        <v>11.6520282604646</v>
+      </c>
+      <c r="X8" s="19" t="n">
+        <f aca="false">X7+(B8-B7)/((W8+W7)/2)</f>
+        <v>0.357546751519754</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="49" t="n">
@@ -9780,11 +9903,11 @@
         <v>29842.02</v>
       </c>
       <c r="M9" s="19" t="n">
-        <f aca="false">(K9-E9)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I9-E9)/M_calc,(G9-E9)/(delta_m*M_calc))</f>
         <v>8.21677690749264</v>
       </c>
       <c r="N9" s="19" t="n">
-        <f aca="false">(L9-E9)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J9-E9)/M_calc,(G9-E9)/(delta_m*M_calc))</f>
         <v>11.6502769074926</v>
       </c>
       <c r="O9" s="19" t="n">
@@ -9815,6 +9938,18 @@
         <f aca="false">B9/(2*PI()*r_w)*60*i_g</f>
         <v>866.666666666667</v>
       </c>
+      <c r="V9" s="50" t="n">
+        <f aca="false">IF(B9=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B9))</f>
+        <v>31038.9354174672</v>
+      </c>
+      <c r="W9" s="19" t="n">
+        <f aca="false">MIN((J9-E9)/M_calc,(V9-E9)/(delta_m*M_calc))</f>
+        <v>11.6502769074926</v>
+      </c>
+      <c r="X9" s="19" t="n">
+        <f aca="false">X8+(B9-B8)/((W9+W8)/2)</f>
+        <v>0.476752888327089</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="49" t="n">
@@ -9865,11 +10000,11 @@
         <v>29842.02</v>
       </c>
       <c r="M10" s="19" t="n">
-        <f aca="false">(K10-E10)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I10-E10)/M_calc,(G10-E10)/(delta_m*M_calc))</f>
         <v>8.21452516795724</v>
       </c>
       <c r="N10" s="19" t="n">
-        <f aca="false">(L10-E10)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J10-E10)/M_calc,(G10-E10)/(delta_m*M_calc))</f>
         <v>11.6480251679572</v>
       </c>
       <c r="O10" s="19" t="n">
@@ -9900,6 +10035,18 @@
         <f aca="false">B10/(2*PI()*r_w)*60*i_g</f>
         <v>1083.33333333333</v>
       </c>
+      <c r="V10" s="50" t="n">
+        <f aca="false">IF(B10=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B10))</f>
+        <v>31038.9354174672</v>
+      </c>
+      <c r="W10" s="19" t="n">
+        <f aca="false">MIN((J10-E10)/M_calc,(V10-E10)/(delta_m*M_calc))</f>
+        <v>11.6480251679572</v>
+      </c>
+      <c r="X10" s="19" t="n">
+        <f aca="false">X9+(B10-B9)/((W10+W9)/2)</f>
+        <v>0.595979507021539</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="49" t="n">
@@ -9950,11 +10097,11 @@
         <v>29842.02</v>
       </c>
       <c r="M11" s="19" t="n">
-        <f aca="false">(K11-E11)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I11-E11)/M_calc,(G11-E11)/(delta_m*M_calc))</f>
         <v>8.21177304185843</v>
       </c>
       <c r="N11" s="19" t="n">
-        <f aca="false">(L11-E11)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J11-E11)/M_calc,(G11-E11)/(delta_m*M_calc))</f>
         <v>11.6452730418584</v>
       </c>
       <c r="O11" s="19" t="n">
@@ -9985,6 +10132,18 @@
         <f aca="false">B11/(2*PI()*r_w)*60*i_g</f>
         <v>1300</v>
       </c>
+      <c r="V11" s="50" t="n">
+        <f aca="false">IF(B11=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B11))</f>
+        <v>31038.9354174672</v>
+      </c>
+      <c r="W11" s="19" t="n">
+        <f aca="false">MIN((J11-E11)/M_calc,(V11-E11)/(delta_m*M_calc))</f>
+        <v>11.6452730418584</v>
+      </c>
+      <c r="X11" s="19" t="n">
+        <f aca="false">X10+(B11-B10)/((W11+W10)/2)</f>
+        <v>0.7152317379747</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="49" t="n">
@@ -10035,11 +10194,11 @@
         <v>29842.02</v>
       </c>
       <c r="M12" s="19" t="n">
-        <f aca="false">(K12-E12)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I12-E12)/M_calc,(G12-E12)/(delta_m*M_calc))</f>
         <v>8.20852052919619</v>
       </c>
       <c r="N12" s="19" t="n">
-        <f aca="false">(L12-E12)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J12-E12)/M_calc,(G12-E12)/(delta_m*M_calc))</f>
         <v>11.6420205291962</v>
       </c>
       <c r="O12" s="19" t="n">
@@ -10070,6 +10229,18 @@
         <f aca="false">B12/(2*PI()*r_w)*60*i_g</f>
         <v>1516.66666666667</v>
       </c>
+      <c r="V12" s="50" t="n">
+        <f aca="false">IF(B12=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B12))</f>
+        <v>31038.9354174672</v>
+      </c>
+      <c r="W12" s="19" t="n">
+        <f aca="false">MIN((J12-E12)/M_calc,(V12-E12)/(delta_m*M_calc))</f>
+        <v>11.6420205291962</v>
+      </c>
+      <c r="X12" s="19" t="n">
+        <f aca="false">X11+(B12-B11)/((W12+W11)/2)</f>
+        <v>0.834514718167403</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="49" t="n">
@@ -10120,11 +10291,11 @@
         <v>29842.02</v>
       </c>
       <c r="M13" s="19" t="n">
-        <f aca="false">(K13-E13)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I13-E13)/M_calc,(G13-E13)/(delta_m*M_calc))</f>
         <v>8.20476762997054</v>
       </c>
       <c r="N13" s="19" t="n">
-        <f aca="false">(L13-E13)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J13-E13)/M_calc,(G13-E13)/(delta_m*M_calc))</f>
         <v>11.6382676299705</v>
       </c>
       <c r="O13" s="19" t="n">
@@ -10155,6 +10326,18 @@
         <f aca="false">B13/(2*PI()*r_w)*60*i_g</f>
         <v>1733.33333333333</v>
       </c>
+      <c r="V13" s="50" t="n">
+        <f aca="false">IF(B13=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B13))</f>
+        <v>31038.9354174672</v>
+      </c>
+      <c r="W13" s="19" t="n">
+        <f aca="false">MIN((J13-E13)/M_calc,(V13-E13)/(delta_m*M_calc))</f>
+        <v>11.6382676299705</v>
+      </c>
+      <c r="X13" s="19" t="n">
+        <f aca="false">X12+(B13-B12)/((W13+W12)/2)</f>
+        <v>0.953833592520941</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="49" t="n">
@@ -10205,11 +10388,11 @@
         <v>29842.02</v>
       </c>
       <c r="M14" s="19" t="n">
-        <f aca="false">(K14-E14)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I14-E14)/M_calc,(G14-E14)/(delta_m*M_calc))</f>
         <v>8.20051434418146</v>
       </c>
       <c r="N14" s="19" t="n">
-        <f aca="false">(L14-E14)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J14-E14)/M_calc,(G14-E14)/(delta_m*M_calc))</f>
         <v>11.6340143441815</v>
       </c>
       <c r="O14" s="19" t="n">
@@ -10240,6 +10423,18 @@
         <f aca="false">B14/(2*PI()*r_w)*60*i_g</f>
         <v>1950</v>
       </c>
+      <c r="V14" s="50" t="n">
+        <f aca="false">IF(B14=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B14))</f>
+        <v>31038.9354174672</v>
+      </c>
+      <c r="W14" s="19" t="n">
+        <f aca="false">MIN((J14-E14)/M_calc,(V14-E14)/(delta_m*M_calc))</f>
+        <v>11.6340143441815</v>
+      </c>
+      <c r="X14" s="19" t="n">
+        <f aca="false">X13+(B14-B13)/((W14+W13)/2)</f>
+        <v>1.07319351523342</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="49" t="n">
@@ -10290,11 +10485,11 @@
         <v>29842.02</v>
       </c>
       <c r="M15" s="19" t="n">
-        <f aca="false">(K15-E15)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I15-E15)/M_calc,(G15-E15)/(delta_m*M_calc))</f>
         <v>8.19576067182896</v>
       </c>
       <c r="N15" s="19" t="n">
-        <f aca="false">(L15-E15)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J15-E15)/M_calc,(G15-E15)/(delta_m*M_calc))</f>
         <v>11.629260671829</v>
       </c>
       <c r="O15" s="19" t="n">
@@ -10325,6 +10520,18 @@
         <f aca="false">B15/(2*PI()*r_w)*60*i_g</f>
         <v>2166.66666666667</v>
       </c>
+      <c r="V15" s="50" t="n">
+        <f aca="false">IF(B15=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B15))</f>
+        <v>31038.9354174672</v>
+      </c>
+      <c r="W15" s="19" t="n">
+        <f aca="false">MIN((J15-E15)/M_calc,(V15-E15)/(delta_m*M_calc))</f>
+        <v>11.629260671829</v>
+      </c>
+      <c r="X15" s="19" t="n">
+        <f aca="false">X14+(B15-B14)/((W15+W14)/2)</f>
+        <v>1.19259965112211</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="49" t="n">
@@ -10375,11 +10582,11 @@
         <v>29842.02</v>
       </c>
       <c r="M16" s="19" t="n">
-        <f aca="false">(K16-E16)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I16-E16)/M_calc,(G16-E16)/(delta_m*M_calc))</f>
         <v>8.19050661291305</v>
       </c>
       <c r="N16" s="19" t="n">
-        <f aca="false">(L16-E16)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J16-E16)/M_calc,(G16-E16)/(delta_m*M_calc))</f>
         <v>11.624006612913</v>
       </c>
       <c r="O16" s="19" t="n">
@@ -10410,6 +10617,18 @@
         <f aca="false">B16/(2*PI()*r_w)*60*i_g</f>
         <v>2383.33333333333</v>
       </c>
+      <c r="V16" s="50" t="n">
+        <f aca="false">IF(B16=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B16))</f>
+        <v>31038.9354174672</v>
+      </c>
+      <c r="W16" s="19" t="n">
+        <f aca="false">MIN((J16-E16)/M_calc,(V16-E16)/(delta_m*M_calc))</f>
+        <v>11.624006612913</v>
+      </c>
+      <c r="X16" s="19" t="n">
+        <f aca="false">X15+(B16-B15)/((W16+W15)/2)</f>
+        <v>1.3120571769727</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="49" t="n">
@@ -10460,11 +10679,11 @@
         <v>29842.02</v>
       </c>
       <c r="M17" s="19" t="n">
-        <f aca="false">(K17-E17)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I17-E17)/M_calc,(G17-E17)/(delta_m*M_calc))</f>
         <v>8.18475216743371</v>
       </c>
       <c r="N17" s="19" t="n">
-        <f aca="false">(L17-E17)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J17-E17)/M_calc,(G17-E17)/(delta_m*M_calc))</f>
         <v>11.6182521674337</v>
       </c>
       <c r="O17" s="19" t="n">
@@ -10495,6 +10714,18 @@
         <f aca="false">B17/(2*PI()*r_w)*60*i_g</f>
         <v>2600</v>
       </c>
+      <c r="V17" s="50" t="n">
+        <f aca="false">IF(B17=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B17))</f>
+        <v>31038.9354174672</v>
+      </c>
+      <c r="W17" s="19" t="n">
+        <f aca="false">MIN((J17-E17)/M_calc,(V17-E17)/(delta_m*M_calc))</f>
+        <v>11.6182521674337</v>
+      </c>
+      <c r="X17" s="19" t="n">
+        <f aca="false">X16+(B17-B16)/((W17+W16)/2)</f>
+        <v>1.43157128289629</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="49" t="n">
@@ -10545,11 +10776,11 @@
         <v>29842.02</v>
       </c>
       <c r="M18" s="19" t="n">
-        <f aca="false">(K18-E18)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I18-E18)/M_calc,(G18-E18)/(delta_m*M_calc))</f>
         <v>8.17849733539095</v>
       </c>
       <c r="N18" s="19" t="n">
-        <f aca="false">(L18-E18)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J18-E18)/M_calc,(G18-E18)/(delta_m*M_calc))</f>
         <v>11.6119973353909</v>
       </c>
       <c r="O18" s="19" t="n">
@@ -10580,6 +10811,18 @@
         <f aca="false">B18/(2*PI()*r_w)*60*i_g</f>
         <v>2816.66666666667</v>
       </c>
+      <c r="V18" s="50" t="n">
+        <f aca="false">IF(B18=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B18))</f>
+        <v>31038.9354174672</v>
+      </c>
+      <c r="W18" s="19" t="n">
+        <f aca="false">MIN((J18-E18)/M_calc,(V18-E18)/(delta_m*M_calc))</f>
+        <v>11.6119973353909</v>
+      </c>
+      <c r="X18" s="19" t="n">
+        <f aca="false">X17+(B18-B17)/((W18+W17)/2)</f>
+        <v>1.55114717369505</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="49" t="n">
@@ -10630,11 +10873,11 @@
         <v>29842.02</v>
       </c>
       <c r="M19" s="19" t="n">
-        <f aca="false">(K19-E19)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I19-E19)/M_calc,(G19-E19)/(delta_m*M_calc))</f>
         <v>8.17174211678477</v>
       </c>
       <c r="N19" s="19" t="n">
-        <f aca="false">(L19-E19)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J19-E19)/M_calc,(G19-E19)/(delta_m*M_calc))</f>
         <v>11.6052421167848</v>
       </c>
       <c r="O19" s="19" t="n">
@@ -10665,6 +10908,18 @@
         <f aca="false">B19/(2*PI()*r_w)*60*i_g</f>
         <v>3033.33333333333</v>
       </c>
+      <c r="V19" s="50" t="n">
+        <f aca="false">IF(B19=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B19))</f>
+        <v>31038.9354174672</v>
+      </c>
+      <c r="W19" s="19" t="n">
+        <f aca="false">MIN((J19-E19)/M_calc,(V19-E19)/(delta_m*M_calc))</f>
+        <v>11.6052421167848</v>
+      </c>
+      <c r="X19" s="19" t="n">
+        <f aca="false">X18+(B19-B18)/((W19+W18)/2)</f>
+        <v>1.6707900702375</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="49" t="n">
@@ -10715,11 +10970,11 @@
         <v>29842.02</v>
       </c>
       <c r="M20" s="19" t="n">
-        <f aca="false">(K20-E20)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I20-E20)/M_calc,(G20-E20)/(delta_m*M_calc))</f>
         <v>8.16448651161517</v>
       </c>
       <c r="N20" s="19" t="n">
-        <f aca="false">(L20-E20)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J20-E20)/M_calc,(G20-E20)/(delta_m*M_calc))</f>
         <v>11.5979865116152</v>
       </c>
       <c r="O20" s="19" t="n">
@@ -10750,6 +11005,18 @@
         <f aca="false">B20/(2*PI()*r_w)*60*i_g</f>
         <v>3250</v>
       </c>
+      <c r="V20" s="50" t="n">
+        <f aca="false">IF(B20=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B20))</f>
+        <v>31038.9354174672</v>
+      </c>
+      <c r="W20" s="19" t="n">
+        <f aca="false">MIN((J20-E20)/M_calc,(V20-E20)/(delta_m*M_calc))</f>
+        <v>11.5979865116152</v>
+      </c>
+      <c r="X20" s="19" t="n">
+        <f aca="false">X19+(B20-B19)/((W20+W19)/2)</f>
+        <v>1.79050521084417</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="49" t="n">
@@ -10800,11 +11067,11 @@
         <v>29842.02</v>
       </c>
       <c r="M21" s="19" t="n">
-        <f aca="false">(K21-E21)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I21-E21)/M_calc,(G21-E21)/(delta_m*M_calc))</f>
         <v>8.15673051988214</v>
       </c>
       <c r="N21" s="19" t="n">
-        <f aca="false">(L21-E21)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J21-E21)/M_calc,(G21-E21)/(delta_m*M_calc))</f>
         <v>11.5902305198821</v>
       </c>
       <c r="O21" s="19" t="n">
@@ -10835,6 +11102,18 @@
         <f aca="false">B21/(2*PI()*r_w)*60*i_g</f>
         <v>3466.66666666667</v>
       </c>
+      <c r="V21" s="50" t="n">
+        <f aca="false">IF(B21=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B21))</f>
+        <v>31038.9354174672</v>
+      </c>
+      <c r="W21" s="19" t="n">
+        <f aca="false">MIN((J21-E21)/M_calc,(V21-E21)/(delta_m*M_calc))</f>
+        <v>11.5902305198821</v>
+      </c>
+      <c r="X21" s="19" t="n">
+        <f aca="false">X20+(B21-B20)/((W21+W20)/2)</f>
+        <v>1.91029785268484</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="49" t="n">
@@ -10885,11 +11164,11 @@
         <v>29842.02</v>
       </c>
       <c r="M22" s="19" t="n">
-        <f aca="false">(K22-E22)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I22-E22)/M_calc,(G22-E22)/(delta_m*M_calc))</f>
         <v>8.1484741415857</v>
       </c>
       <c r="N22" s="19" t="n">
-        <f aca="false">(L22-E22)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J22-E22)/M_calc,(G22-E22)/(delta_m*M_calc))</f>
         <v>11.5819741415857</v>
       </c>
       <c r="O22" s="19" t="n">
@@ -10920,6 +11199,18 @@
         <f aca="false">B22/(2*PI()*r_w)*60*i_g</f>
         <v>3683.33333333333</v>
       </c>
+      <c r="V22" s="50" t="n">
+        <f aca="false">IF(B22=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B22))</f>
+        <v>30176.4705882353</v>
+      </c>
+      <c r="W22" s="19" t="n">
+        <f aca="false">MIN((J22-E22)/M_calc,(V22-E22)/(delta_m*M_calc))</f>
+        <v>11.5819741415857</v>
+      </c>
+      <c r="X22" s="19" t="n">
+        <f aca="false">X21+(B22-B21)/((W22+W21)/2)</f>
+        <v>2.03017327318796</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="49" t="n">
@@ -10970,11 +11261,11 @@
         <v>29842.02</v>
       </c>
       <c r="M23" s="19" t="n">
-        <f aca="false">(K23-E23)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I23-E23)/M_calc,(G23-E23)/(delta_m*M_calc))</f>
         <v>8.13971737672584</v>
       </c>
       <c r="N23" s="19" t="n">
-        <f aca="false">(L23-E23)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J23-E23)/M_calc,(G23-E23)/(delta_m*M_calc))</f>
         <v>11.5732173767258</v>
       </c>
       <c r="O23" s="19" t="n">
@@ -11005,6 +11296,18 @@
         <f aca="false">B23/(2*PI()*r_w)*60*i_g</f>
         <v>3900</v>
       </c>
+      <c r="V23" s="50" t="n">
+        <f aca="false">IF(B23=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B23))</f>
+        <v>28500</v>
+      </c>
+      <c r="W23" s="19" t="n">
+        <f aca="false">MIN((J23-E23)/M_calc,(V23-E23)/(delta_m*M_calc))</f>
+        <v>11.0438209270217</v>
+      </c>
+      <c r="X23" s="19" t="n">
+        <f aca="false">X22+(B23-B22)/((W23+W22)/2)</f>
+        <v>2.15294366730471</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="49" t="n">
@@ -11055,11 +11358,11 @@
         <v>29842.02</v>
       </c>
       <c r="M24" s="19" t="n">
-        <f aca="false">(K24-E24)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I24-E24)/M_calc,(G24-E24)/(delta_m*M_calc))</f>
         <v>8.13046022530256</v>
       </c>
       <c r="N24" s="19" t="n">
-        <f aca="false">(L24-E24)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J24-E24)/M_calc,(G24-E24)/(delta_m*M_calc))</f>
         <v>11.5639602253026</v>
       </c>
       <c r="O24" s="19" t="n">
@@ -11090,6 +11393,18 @@
         <f aca="false">B24/(2*PI()*r_w)*60*i_g</f>
         <v>4116.66666666667</v>
       </c>
+      <c r="V24" s="50" t="n">
+        <f aca="false">IF(B24=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B24))</f>
+        <v>27000</v>
+      </c>
+      <c r="W24" s="19" t="n">
+        <f aca="false">MIN((J24-E24)/M_calc,(V24-E24)/(delta_m*M_calc))</f>
+        <v>10.4428477992671</v>
+      </c>
+      <c r="X24" s="19" t="n">
+        <f aca="false">X23+(B24-B23)/((W24+W23)/2)</f>
+        <v>2.2822227944306</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="49" t="n">
@@ -11140,11 +11455,11 @@
         <v>29412</v>
       </c>
       <c r="M25" s="19" t="n">
-        <f aca="false">(K25-E25)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I25-E25)/M_calc,(G25-E25)/(delta_m*M_calc))</f>
         <v>8.12070268731585</v>
       </c>
       <c r="N25" s="19" t="n">
-        <f aca="false">(L25-E25)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J25-E25)/M_calc,(G25-E25)/(delta_m*M_calc))</f>
         <v>11.3845695512212</v>
       </c>
       <c r="O25" s="19" t="n">
@@ -11175,6 +11490,18 @@
         <f aca="false">B25/(2*PI()*r_w)*60*i_g</f>
         <v>4333.33333333333</v>
       </c>
+      <c r="V25" s="50" t="n">
+        <f aca="false">IF(B25=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B25))</f>
+        <v>25650</v>
+      </c>
+      <c r="W25" s="19" t="n">
+        <f aca="false">MIN((J25-E25)/M_calc,(V25-E25)/(delta_m*M_calc))</f>
+        <v>9.90054588258212</v>
+      </c>
+      <c r="X25" s="19" t="n">
+        <f aca="false">X24+(B25-B24)/((W25+W24)/2)</f>
+        <v>2.41876725801517</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="49" t="n">
@@ -11225,11 +11552,11 @@
         <v>28011.4285714286</v>
       </c>
       <c r="M26" s="19" t="n">
-        <f aca="false">(K26-E26)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I26-E26)/M_calc,(G26-E26)/(delta_m*M_calc))</f>
         <v>8.11044476276572</v>
       </c>
       <c r="N26" s="19" t="n">
-        <f aca="false">(L26-E26)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J26-E26)/M_calc,(G26-E26)/(delta_m*M_calc))</f>
         <v>10.8218179664851</v>
       </c>
       <c r="O26" s="19" t="n">
@@ -11260,6 +11587,18 @@
         <f aca="false">B26/(2*PI()*r_w)*60*i_g</f>
         <v>4550</v>
       </c>
+      <c r="V26" s="50" t="n">
+        <f aca="false">IF(B26=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B26))</f>
+        <v>24428.5714285714</v>
+      </c>
+      <c r="W26" s="19" t="n">
+        <f aca="false">MIN((J26-E26)/M_calc,(V26-E26)/(delta_m*M_calc))</f>
+        <v>9.40846209159075</v>
+      </c>
+      <c r="X26" s="19" t="n">
+        <f aca="false">X25+(B26-B25)/((W26+W25)/2)</f>
+        <v>2.56262642372131</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="49" t="n">
@@ -11310,11 +11649,11 @@
         <v>26738.1818181818</v>
       </c>
       <c r="M27" s="19" t="n">
-        <f aca="false">(K27-E27)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I27-E27)/M_calc,(G27-E27)/(delta_m*M_calc))</f>
         <v>8.09968645165218</v>
       </c>
       <c r="N27" s="19" t="n">
-        <f aca="false">(L27-E27)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J27-E27)/M_calc,(G27-E27)/(delta_m*M_calc))</f>
         <v>10.3087926915661</v>
       </c>
       <c r="O27" s="19" t="n">
@@ -11345,6 +11684,18 @@
         <f aca="false">B27/(2*PI()*r_w)*60*i_g</f>
         <v>4766.66666666667</v>
       </c>
+      <c r="V27" s="50" t="n">
+        <f aca="false">IF(B27=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B27))</f>
+        <v>23318.1818181818</v>
+      </c>
+      <c r="W27" s="19" t="n">
+        <f aca="false">MIN((J27-E27)/M_calc,(V27-E27)/(delta_m*M_calc))</f>
+        <v>8.95968026553061</v>
+      </c>
+      <c r="X27" s="19" t="n">
+        <f aca="false">X26+(B27-B26)/((W27+W26)/2)</f>
+        <v>2.71385444252534</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="n">
@@ -11395,11 +11746,11 @@
         <v>25575.652173913</v>
       </c>
       <c r="M28" s="19" t="n">
-        <f aca="false">(K28-E28)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I28-E28)/M_calc,(G28-E28)/(delta_m*M_calc))</f>
         <v>8.08842775397521</v>
       </c>
       <c r="N28" s="19" t="n">
-        <f aca="false">(L28-E28)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J28-E28)/M_calc,(G28-E28)/(delta_m*M_calc))</f>
         <v>9.83894241824071</v>
       </c>
       <c r="O28" s="19" t="n">
@@ -11430,6 +11781,18 @@
         <f aca="false">B28/(2*PI()*r_w)*60*i_g</f>
         <v>4983.33333333333</v>
       </c>
+      <c r="V28" s="50" t="n">
+        <f aca="false">IF(B28=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B28))</f>
+        <v>22304.347826087</v>
+      </c>
+      <c r="W28" s="19" t="n">
+        <f aca="false">MIN((J28-E28)/M_calc,(V28-E28)/(delta_m*M_calc))</f>
+        <v>8.54848705420675</v>
+      </c>
+      <c r="X28" s="19" t="n">
+        <f aca="false">X27+(B28-B27)/((W28+W27)/2)</f>
+        <v>2.87251055581518</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="49" t="n">
@@ -11480,11 +11843,11 @@
         <v>24510</v>
       </c>
       <c r="M29" s="19" t="n">
-        <f aca="false">(K29-E29)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I29-E29)/M_calc,(G29-E29)/(delta_m*M_calc))</f>
         <v>8.07666866973482</v>
       </c>
       <c r="N29" s="19" t="n">
-        <f aca="false">(L29-E29)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J29-E29)/M_calc,(G29-E29)/(delta_m*M_calc))</f>
         <v>9.40680772298926</v>
       </c>
       <c r="O29" s="19" t="n">
@@ -11515,6 +11878,18 @@
         <f aca="false">B29/(2*PI()*r_w)*60*i_g</f>
         <v>5200</v>
       </c>
+      <c r="V29" s="50" t="n">
+        <f aca="false">IF(B29=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B29))</f>
+        <v>21375</v>
+      </c>
+      <c r="W29" s="19" t="n">
+        <f aca="false">MIN((J29-E29)/M_calc,(V29-E29)/(delta_m*M_calc))</f>
+        <v>8.17012133245672</v>
+      </c>
+      <c r="X29" s="19" t="n">
+        <f aca="false">X28+(B29-B28)/((W29+W28)/2)</f>
+        <v>3.03865941901803</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="49" t="n">
@@ -11565,11 +11940,11 @@
         <v>23529.6</v>
       </c>
       <c r="M30" s="19" t="n">
-        <f aca="false">(K30-E30)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I30-E30)/M_calc,(G30-E30)/(delta_m*M_calc))</f>
         <v>8.06440919893102</v>
       </c>
       <c r="N30" s="19" t="n">
-        <f aca="false">(L30-E30)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J30-E30)/M_calc,(G30-E30)/(delta_m*M_calc))</f>
         <v>9.00780269005528</v>
       </c>
       <c r="O30" s="19" t="n">
@@ -11600,6 +11975,18 @@
         <f aca="false">B30/(2*PI()*r_w)*60*i_g</f>
         <v>5416.66666666667</v>
       </c>
+      <c r="V30" s="50" t="n">
+        <f aca="false">IF(B30=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B30))</f>
+        <v>20520</v>
+      </c>
+      <c r="W30" s="19" t="n">
+        <f aca="false">MIN((J30-E30)/M_calc,(V30-E30)/(delta_m*M_calc))</f>
+        <v>7.82058375514403</v>
+      </c>
+      <c r="X30" s="19" t="n">
+        <f aca="false">X29+(B30-B29)/((W30+W29)/2)</f>
+        <v>3.21237144500816</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="49" t="n">
@@ -11650,11 +12037,11 @@
         <v>22624.6153846154</v>
       </c>
       <c r="M31" s="19" t="n">
-        <f aca="false">(K31-E31)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I31-E31)/M_calc,(G31-E31)/(delta_m*M_calc))</f>
         <v>8.05164934156379</v>
       </c>
       <c r="N31" s="19" t="n">
-        <f aca="false">(L31-E31)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J31-E31)/M_calc,(G31-E31)/(delta_m*M_calc))</f>
         <v>8.63804692918327</v>
       </c>
       <c r="O31" s="19" t="n">
@@ -11685,6 +12072,18 @@
         <f aca="false">B31/(2*PI()*r_w)*60*i_g</f>
         <v>5633.33333333333</v>
       </c>
+      <c r="V31" s="50" t="n">
+        <f aca="false">IF(B31=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B31))</f>
+        <v>19730.7692307692</v>
+      </c>
+      <c r="W31" s="19" t="n">
+        <f aca="false">MIN((J31-E31)/M_calc,(V31-E31)/(delta_m*M_calc))</f>
+        <v>7.49649026099938</v>
+      </c>
+      <c r="X31" s="19" t="n">
+        <f aca="false">X30+(B31-B30)/((W31+W30)/2)</f>
+        <v>3.39372316889812</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="49" t="n">
@@ -11735,11 +12134,11 @@
         <v>21786.6666666667</v>
       </c>
       <c r="M32" s="19" t="n">
-        <f aca="false">(K32-E32)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I32-E32)/M_calc,(G32-E32)/(delta_m*M_calc))</f>
         <v>8.03838909763314</v>
       </c>
       <c r="N32" s="19" t="n">
-        <f aca="false">(L32-E32)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J32-E32)/M_calc,(G32-E32)/(delta_m*M_calc))</f>
         <v>8.29423492274819</v>
       </c>
       <c r="O32" s="19" t="n">
@@ -11770,6 +12169,18 @@
         <f aca="false">B32/(2*PI()*r_w)*60*i_g</f>
         <v>5850</v>
       </c>
+      <c r="V32" s="50" t="n">
+        <f aca="false">IF(B32=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B32))</f>
+        <v>19000</v>
+      </c>
+      <c r="W32" s="19" t="n">
+        <f aca="false">MIN((J32-E32)/M_calc,(V32-E32)/(delta_m*M_calc))</f>
+        <v>7.19495813116371</v>
+      </c>
+      <c r="X32" s="19" t="n">
+        <f aca="false">X31+(B32-B31)/((W32+W31)/2)</f>
+        <v>3.58279763614123</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="49" t="n">
@@ -11820,11 +12231,11 @@
         <v>21008.5714285714</v>
       </c>
       <c r="M33" s="19" t="n">
-        <f aca="false">(K33-E33)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I33-E33)/M_calc,(G33-E33)/(delta_m*M_calc))</f>
         <v>7.97353336992858</v>
       </c>
       <c r="N33" s="19" t="n">
-        <f aca="false">(L33-E33)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J33-E33)/M_calc,(G33-E33)/(delta_m*M_calc))</f>
         <v>7.97353336992858</v>
       </c>
       <c r="O33" s="19" t="n">
@@ -11855,6 +12266,18 @@
         <f aca="false">B33/(2*PI()*r_w)*60*i_g</f>
         <v>6066.66666666667</v>
       </c>
+      <c r="V33" s="50" t="n">
+        <f aca="false">IF(B33=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B33))</f>
+        <v>18321.4285714286</v>
+      </c>
+      <c r="W33" s="19" t="n">
+        <f aca="false">MIN((J33-E33)/M_calc,(V33-E33)/(delta_m*M_calc))</f>
+        <v>6.91351646375783</v>
+      </c>
+      <c r="X33" s="19" t="n">
+        <f aca="false">X32+(B33-B32)/((W33+W32)/2)</f>
+        <v>3.77968481618957</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="49" t="n">
@@ -11905,11 +12328,11 @@
         <v>20284.1379310345</v>
       </c>
       <c r="M34" s="19" t="n">
-        <f aca="false">(K34-E34)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I34-E34)/M_calc,(G34-E34)/(delta_m*M_calc))</f>
         <v>7.67349977001628</v>
       </c>
       <c r="N34" s="19" t="n">
-        <f aca="false">(L34-E34)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J34-E34)/M_calc,(G34-E34)/(delta_m*M_calc))</f>
         <v>7.67349977001628</v>
       </c>
       <c r="O34" s="19" t="n">
@@ -11940,6 +12363,18 @@
         <f aca="false">B34/(2*PI()*r_w)*60*i_g</f>
         <v>6283.33333333333</v>
       </c>
+      <c r="V34" s="50" t="n">
+        <f aca="false">IF(B34=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B34))</f>
+        <v>17689.6551724138</v>
+      </c>
+      <c r="W34" s="19" t="n">
+        <f aca="false">MIN((J34-E34)/M_calc,(V34-E34)/(delta_m*M_calc))</f>
+        <v>6.65003517095487</v>
+      </c>
+      <c r="X34" s="19" t="n">
+        <f aca="false">X33+(B34-B33)/((W34+W33)/2)</f>
+        <v>3.98448204427463</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="49" t="n">
@@ -11990,11 +12425,11 @@
         <v>19608</v>
       </c>
       <c r="M35" s="19" t="n">
-        <f aca="false">(K35-E35)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I35-E35)/M_calc,(G35-E35)/(delta_m*M_calc))</f>
         <v>7.39201728906421</v>
       </c>
       <c r="N35" s="19" t="n">
-        <f aca="false">(L35-E35)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J35-E35)/M_calc,(G35-E35)/(delta_m*M_calc))</f>
         <v>7.39201728906421</v>
       </c>
       <c r="O35" s="19" t="n">
@@ -12025,6 +12460,18 @@
         <f aca="false">B35/(2*PI()*r_w)*60*i_g</f>
         <v>6500</v>
       </c>
+      <c r="V35" s="50" t="n">
+        <f aca="false">IF(B35=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B35))</f>
+        <v>17100</v>
+      </c>
+      <c r="W35" s="19" t="n">
+        <f aca="false">MIN((J35-E35)/M_calc,(V35-E35)/(delta_m*M_calc))</f>
+        <v>6.40266817663818</v>
+      </c>
+      <c r="X35" s="19" t="n">
+        <f aca="false">X34+(B35-B34)/((W35+W34)/2)</f>
+        <v>4.19729449421742</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="49" t="n">
@@ -12075,11 +12522,11 @@
         <v>18975.4838709677</v>
       </c>
       <c r="M36" s="19" t="n">
-        <f aca="false">(K36-E36)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I36-E36)/M_calc,(G36-E36)/(delta_m*M_calc))</f>
         <v>7.12724223298944</v>
       </c>
       <c r="N36" s="19" t="n">
-        <f aca="false">(L36-E36)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J36-E36)/M_calc,(G36-E36)/(delta_m*M_calc))</f>
         <v>7.12724223298944</v>
       </c>
       <c r="O36" s="19" t="n">
@@ -12110,6 +12557,18 @@
         <f aca="false">B36/(2*PI()*r_w)*60*i_g</f>
         <v>6716.66666666667</v>
       </c>
+      <c r="V36" s="50" t="n">
+        <f aca="false">IF(B36=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B36))</f>
+        <v>16548.3870967742</v>
+      </c>
+      <c r="W36" s="19" t="n">
+        <f aca="false">MIN((J36-E36)/M_calc,(V36-E36)/(delta_m*M_calc))</f>
+        <v>6.16980760806102</v>
+      </c>
+      <c r="X36" s="19" t="n">
+        <f aca="false">X35+(B36-B35)/((W36+W35)/2)</f>
+        <v>4.41823568554255</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="49" t="n">
@@ -12160,11 +12619,11 @@
         <v>18382.5</v>
       </c>
       <c r="M37" s="19" t="n">
-        <f aca="false">(K37-E37)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I37-E37)/M_calc,(G37-E37)/(delta_m*M_calc))</f>
         <v>6.8775613694694</v>
       </c>
       <c r="N37" s="19" t="n">
-        <f aca="false">(L37-E37)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J37-E37)/M_calc,(G37-E37)/(delta_m*M_calc))</f>
         <v>6.8775613694694</v>
       </c>
       <c r="O37" s="19" t="n">
@@ -12195,6 +12654,18 @@
         <f aca="false">B37/(2*PI()*r_w)*60*i_g</f>
         <v>6933.33333333333</v>
       </c>
+      <c r="V37" s="50" t="n">
+        <f aca="false">IF(B37=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B37))</f>
+        <v>16031.25</v>
+      </c>
+      <c r="W37" s="19" t="n">
+        <f aca="false">MIN((J37-E37)/M_calc,(V37-E37)/(delta_m*M_calc))</f>
+        <v>5.95004657657</v>
+      </c>
+      <c r="X37" s="19" t="n">
+        <f aca="false">X36+(B37-B36)/((W37+W36)/2)</f>
+        <v>4.64742802857422</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="49" t="n">
@@ -12245,11 +12716,11 @@
         <v>17825.4545454545</v>
       </c>
       <c r="M38" s="19" t="n">
-        <f aca="false">(K38-E38)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I38-E38)/M_calc,(G38-E38)/(delta_m*M_calc))</f>
         <v>6.64155700949336</v>
       </c>
       <c r="N38" s="19" t="n">
-        <f aca="false">(L38-E38)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J38-E38)/M_calc,(G38-E38)/(delta_m*M_calc))</f>
         <v>6.64155700949336</v>
       </c>
       <c r="O38" s="19" t="n">
@@ -12280,6 +12751,18 @@
         <f aca="false">B38/(2*PI()*r_w)*60*i_g</f>
         <v>7150</v>
       </c>
+      <c r="V38" s="50" t="n">
+        <f aca="false">IF(B38=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B38))</f>
+        <v>15545.4545454545</v>
+      </c>
+      <c r="W38" s="19" t="n">
+        <f aca="false">MIN((J38-E38)/M_calc,(V38-E38)/(delta_m*M_calc))</f>
+        <v>5.74214872546969</v>
+      </c>
+      <c r="X38" s="19" t="n">
+        <f aca="false">X37+(B38-B37)/((W38+W37)/2)</f>
+        <v>4.88500341164135</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="49" t="n">
@@ -12330,11 +12813,11 @@
         <v>17301.1764705882</v>
       </c>
       <c r="M39" s="19" t="n">
-        <f aca="false">(K39-E39)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I39-E39)/M_calc,(G39-E39)/(delta_m*M_calc))</f>
         <v>6.417978250993</v>
       </c>
       <c r="N39" s="19" t="n">
-        <f aca="false">(L39-E39)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J39-E39)/M_calc,(G39-E39)/(delta_m*M_calc))</f>
         <v>6.417978250993</v>
       </c>
       <c r="O39" s="19" t="n">
@@ -12365,6 +12848,18 @@
         <f aca="false">B39/(2*PI()*r_w)*60*i_g</f>
         <v>7366.66666666667</v>
       </c>
+      <c r="V39" s="50" t="n">
+        <f aca="false">IF(B39=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B39))</f>
+        <v>15088.2352941176</v>
+      </c>
+      <c r="W39" s="19" t="n">
+        <f aca="false">MIN((J39-E39)/M_calc,(V39-E39)/(delta_m*M_calc))</f>
+        <v>5.54502315179355</v>
+      </c>
+      <c r="X39" s="19" t="n">
+        <f aca="false">X38+(B39-B38)/((W39+W38)/2)</f>
+        <v>5.13110383502317</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="49" t="n">
@@ -12415,11 +12910,11 @@
         <v>16806.8571428571</v>
       </c>
       <c r="M40" s="19" t="n">
-        <f aca="false">(K40-E40)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I40-E40)/M_calc,(G40-E40)/(delta_m*M_calc))</f>
         <v>6.20571715213641</v>
       </c>
       <c r="N40" s="19" t="n">
-        <f aca="false">(L40-E40)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J40-E40)/M_calc,(G40-E40)/(delta_m*M_calc))</f>
         <v>6.20571715213641</v>
       </c>
       <c r="O40" s="19" t="n">
@@ -12450,6 +12945,18 @@
         <f aca="false">B40/(2*PI()*r_w)*60*i_g</f>
         <v>7583.33333333333</v>
       </c>
+      <c r="V40" s="50" t="n">
+        <f aca="false">IF(B40=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B40))</f>
+        <v>14657.1428571429</v>
+      </c>
+      <c r="W40" s="19" t="n">
+        <f aca="false">MIN((J40-E40)/M_calc,(V40-E40)/(delta_m*M_calc))</f>
+        <v>5.3577036271998</v>
+      </c>
+      <c r="X40" s="19" t="n">
+        <f aca="false">X39+(B40-B39)/((W40+W39)/2)</f>
+        <v>5.38588209683651</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="49" t="n">
@@ -12500,11 +13007,11 @@
         <v>16340</v>
       </c>
       <c r="M41" s="19" t="n">
-        <f aca="false">(K41-E41)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I41-E41)/M_calc,(G41-E41)/(delta_m*M_calc))</f>
         <v>6.00378887573965</v>
       </c>
       <c r="N41" s="19" t="n">
-        <f aca="false">(L41-E41)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J41-E41)/M_calc,(G41-E41)/(delta_m*M_calc))</f>
         <v>6.00378887573965</v>
       </c>
       <c r="O41" s="19" t="n">
@@ -12535,6 +13042,18 @@
         <f aca="false">B41/(2*PI()*r_w)*60*i_g</f>
         <v>7800</v>
       </c>
+      <c r="V41" s="50" t="n">
+        <f aca="false">IF(B41=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B41))</f>
+        <v>14250</v>
+      </c>
+      <c r="W41" s="19" t="n">
+        <f aca="false">MIN((J41-E41)/M_calc,(V41-E41)/(delta_m*M_calc))</f>
+        <v>5.17933128205128</v>
+      </c>
+      <c r="X41" s="19" t="n">
+        <f aca="false">X40+(B41-B40)/((W41+W40)/2)</f>
+        <v>5.64950253671368</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="49" t="n">
@@ -12585,11 +13104,11 @@
         <v>15898.3783783784</v>
       </c>
       <c r="M42" s="19" t="n">
-        <f aca="false">(K42-E42)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I42-E42)/M_calc,(G42-E42)/(delta_m*M_calc))</f>
         <v>5.81131505350354</v>
       </c>
       <c r="N42" s="19" t="n">
-        <f aca="false">(L42-E42)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J42-E42)/M_calc,(G42-E42)/(delta_m*M_calc))</f>
         <v>5.81131505350354</v>
       </c>
       <c r="O42" s="19" t="n">
@@ -12620,6 +13139,18 @@
         <f aca="false">B42/(2*PI()*r_w)*60*i_g</f>
         <v>8016.66666666667</v>
       </c>
+      <c r="V42" s="50" t="n">
+        <f aca="false">IF(B42=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B42))</f>
+        <v>13864.8648648649</v>
+      </c>
+      <c r="W42" s="19" t="n">
+        <f aca="false">MIN((J42-E42)/M_calc,(V42-E42)/(delta_m*M_calc))</f>
+        <v>5.00914009748243</v>
+      </c>
+      <c r="X42" s="19" t="n">
+        <f aca="false">X41+(B42-B41)/((W42+W41)/2)</f>
+        <v>5.92214184385819</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="49" t="n">
@@ -12670,11 +13201,11 @@
         <v>15480</v>
       </c>
       <c r="M43" s="19" t="n">
-        <f aca="false">(K43-E43)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I43-E43)/M_calc,(G43-E43)/(delta_m*M_calc))</f>
         <v>5.62750977694986</v>
       </c>
       <c r="N43" s="19" t="n">
-        <f aca="false">(L43-E43)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J43-E43)/M_calc,(G43-E43)/(delta_m*M_calc))</f>
         <v>5.62750977694986</v>
       </c>
       <c r="O43" s="19" t="n">
@@ -12705,6 +13236,18 @@
         <f aca="false">B43/(2*PI()*r_w)*60*i_g</f>
         <v>8233.33333333333</v>
       </c>
+      <c r="V43" s="50" t="n">
+        <f aca="false">IF(B43=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B43))</f>
+        <v>13500</v>
+      </c>
+      <c r="W43" s="19" t="n">
+        <f aca="false">MIN((J43-E43)/M_calc,(V43-E43)/(delta_m*M_calc))</f>
+        <v>4.84644468819247</v>
+      </c>
+      <c r="X43" s="19" t="n">
+        <f aca="false">X42+(B43-B42)/((W43+W42)/2)</f>
+        <v>6.20398993691252</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="49" t="n">
@@ -12755,11 +13298,11 @@
         <v>15083.0769230769</v>
       </c>
       <c r="M44" s="19" t="n">
-        <f aca="false">(K44-E44)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I44-E44)/M_calc,(G44-E44)/(delta_m*M_calc))</f>
         <v>5.45166774359817</v>
       </c>
       <c r="N44" s="19" t="n">
-        <f aca="false">(L44-E44)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J44-E44)/M_calc,(G44-E44)/(delta_m*M_calc))</f>
         <v>5.45166774359817</v>
       </c>
       <c r="O44" s="19" t="n">
@@ -12790,6 +13333,18 @@
         <f aca="false">B44/(2*PI()*r_w)*60*i_g</f>
         <v>8450</v>
       </c>
+      <c r="V44" s="50" t="n">
+        <f aca="false">IF(B44=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B44))</f>
+        <v>13153.8461538462</v>
+      </c>
+      <c r="W44" s="19" t="n">
+        <f aca="false">MIN((J44-E44)/M_calc,(V44-E44)/(delta_m*M_calc))</f>
+        <v>4.69062996480892</v>
+      </c>
+      <c r="X44" s="19" t="n">
+        <f aca="false">X43+(B44-B43)/((W44+W43)/2)</f>
+        <v>6.49525092404379</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="49" t="n">
@@ -12840,11 +13395,11 @@
         <v>14706</v>
       </c>
       <c r="M45" s="19" t="n">
-        <f aca="false">(K45-E45)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I45-E45)/M_calc,(G45-E45)/(delta_m*M_calc))</f>
         <v>5.28315418121606</v>
       </c>
       <c r="N45" s="19" t="n">
-        <f aca="false">(L45-E45)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J45-E45)/M_calc,(G45-E45)/(delta_m*M_calc))</f>
         <v>5.28315418121606</v>
       </c>
       <c r="O45" s="19" t="n">
@@ -12875,6 +13430,18 @@
         <f aca="false">B45/(2*PI()*r_w)*60*i_g</f>
         <v>8666.66666666667</v>
       </c>
+      <c r="V45" s="50" t="n">
+        <f aca="false">IF(B45=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B45))</f>
+        <v>12825</v>
+      </c>
+      <c r="W45" s="19" t="n">
+        <f aca="false">MIN((J45-E45)/M_calc,(V45-E45)/(delta_m*M_calc))</f>
+        <v>4.54114234689653</v>
+      </c>
+      <c r="X45" s="19" t="n">
+        <f aca="false">X44+(B45-B44)/((W45+W44)/2)</f>
+        <v>6.79614415277472</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="49" t="n">
@@ -12925,11 +13492,11 @@
         <v>14347.3170731707</v>
       </c>
       <c r="M46" s="19" t="n">
-        <f aca="false">(K46-E46)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I46-E46)/M_calc,(G46-E46)/(delta_m*M_calc))</f>
         <v>5.12139624656941</v>
       </c>
       <c r="N46" s="19" t="n">
-        <f aca="false">(L46-E46)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J46-E46)/M_calc,(G46-E46)/(delta_m*M_calc))</f>
         <v>5.12139624656941</v>
       </c>
       <c r="O46" s="19" t="n">
@@ -12960,6 +13527,18 @@
         <f aca="false">B46/(2*PI()*r_w)*60*i_g</f>
         <v>8883.33333333333</v>
       </c>
+      <c r="V46" s="50" t="n">
+        <f aca="false">IF(B46=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B46))</f>
+        <v>12512.1951219512</v>
+      </c>
+      <c r="W46" s="19" t="n">
+        <f aca="false">MIN((J46-E46)/M_calc,(V46-E46)/(delta_m*M_calc))</f>
+        <v>4.39748226186743</v>
+      </c>
+      <c r="X46" s="19" t="n">
+        <f aca="false">X45+(B46-B45)/((W46+W45)/2)</f>
+        <v>7.10690536038313</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="49" t="n">
@@ -13010,11 +13589,11 @@
         <v>14005.7142857143</v>
       </c>
       <c r="M47" s="19" t="n">
-        <f aca="false">(K47-E47)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I47-E47)/M_calc,(G47-E47)/(delta_m*M_calc))</f>
         <v>4.96587565292258</v>
       </c>
       <c r="N47" s="19" t="n">
-        <f aca="false">(L47-E47)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J47-E47)/M_calc,(G47-E47)/(delta_m*M_calc))</f>
         <v>4.96587565292258</v>
       </c>
       <c r="O47" s="19" t="n">
@@ -13045,6 +13624,18 @@
         <f aca="false">B47/(2*PI()*r_w)*60*i_g</f>
         <v>9100</v>
       </c>
+      <c r="V47" s="50" t="n">
+        <f aca="false">IF(B47=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B47))</f>
+        <v>12214.2857142857</v>
+      </c>
+      <c r="W47" s="19" t="n">
+        <f aca="false">MIN((J47-E47)/M_calc,(V47-E47)/(delta_m*M_calc))</f>
+        <v>4.25919771547541</v>
+      </c>
+      <c r="X47" s="19" t="n">
+        <f aca="false">X46+(B47-B46)/((W47+W46)/2)</f>
+        <v>7.42778793719642</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="49" t="n">
@@ -13095,11 +13686,11 @@
         <v>13680</v>
       </c>
       <c r="M48" s="19" t="n">
-        <f aca="false">(K48-E48)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I48-E48)/M_calc,(G48-E48)/(delta_m*M_calc))</f>
         <v>4.81612232625953</v>
       </c>
       <c r="N48" s="19" t="n">
-        <f aca="false">(L48-E48)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J48-E48)/M_calc,(G48-E48)/(delta_m*M_calc))</f>
         <v>4.81612232625953</v>
       </c>
       <c r="O48" s="19" t="n">
@@ -13130,6 +13721,18 @@
         <f aca="false">B48/(2*PI()*r_w)*60*i_g</f>
         <v>9316.66666666667</v>
       </c>
+      <c r="V48" s="50" t="n">
+        <f aca="false">IF(B48=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B48))</f>
+        <v>11930.2325581395</v>
+      </c>
+      <c r="W48" s="19" t="n">
+        <f aca="false">MIN((J48-E48)/M_calc,(V48-E48)/(delta_m*M_calc))</f>
+        <v>4.12587875945067</v>
+      </c>
+      <c r="X48" s="19" t="n">
+        <f aca="false">X47+(B48-B47)/((W48+W47)/2)</f>
+        <v>7.75906431685547</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="49" t="n">
@@ -13180,11 +13783,11 @@
         <v>13369.0909090909</v>
       </c>
       <c r="M49" s="19" t="n">
-        <f aca="false">(K49-E49)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I49-E49)/M_calc,(G49-E49)/(delta_m*M_calc))</f>
         <v>4.67170892656568</v>
       </c>
       <c r="N49" s="19" t="n">
-        <f aca="false">(L49-E49)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J49-E49)/M_calc,(G49-E49)/(delta_m*M_calc))</f>
         <v>4.67170892656568</v>
       </c>
       <c r="O49" s="19" t="n">
@@ -13215,6 +13818,18 @@
         <f aca="false">B49/(2*PI()*r_w)*60*i_g</f>
         <v>9533.33333333333</v>
       </c>
+      <c r="V49" s="50" t="n">
+        <f aca="false">IF(B49=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B49))</f>
+        <v>11659.0909090909</v>
+      </c>
+      <c r="W49" s="19" t="n">
+        <f aca="false">MIN((J49-E49)/M_calc,(V49-E49)/(delta_m*M_calc))</f>
+        <v>3.99715271354793</v>
+      </c>
+      <c r="X49" s="19" t="n">
+        <f aca="false">X48+(B49-B48)/((W49+W48)/2)</f>
+        <v>8.1010275096624</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="49" t="n">
@@ -13265,11 +13880,11 @@
         <v>13072</v>
       </c>
       <c r="M50" s="19" t="n">
-        <f aca="false">(K50-E50)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I50-E50)/M_calc,(G50-E50)/(delta_m*M_calc))</f>
         <v>4.53224609960552</v>
       </c>
       <c r="N50" s="19" t="n">
-        <f aca="false">(L50-E50)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J50-E50)/M_calc,(G50-E50)/(delta_m*M_calc))</f>
         <v>4.53224609960552</v>
       </c>
       <c r="O50" s="19" t="n">
@@ -13300,6 +13915,18 @@
         <f aca="false">B50/(2*PI()*r_w)*60*i_g</f>
         <v>9750</v>
       </c>
+      <c r="V50" s="50" t="n">
+        <f aca="false">IF(B50=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B50))</f>
+        <v>11400</v>
+      </c>
+      <c r="W50" s="19" t="n">
+        <f aca="false">MIN((J50-E50)/M_calc,(V50-E50)/(delta_m*M_calc))</f>
+        <v>3.87268002465483</v>
+      </c>
+      <c r="X50" s="19" t="n">
+        <f aca="false">X49+(B50-B49)/((W50+W49)/2)</f>
+        <v>8.45399279751325</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="49" t="n">
@@ -13350,11 +13977,11 @@
         <v>12787.8260869565</v>
       </c>
       <c r="M51" s="19" t="n">
-        <f aca="false">(K51-E51)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I51-E51)/M_calc,(G51-E51)/(delta_m*M_calc))</f>
         <v>4.3973783480336</v>
       </c>
       <c r="N51" s="19" t="n">
-        <f aca="false">(L51-E51)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J51-E51)/M_calc,(G51-E51)/(delta_m*M_calc))</f>
         <v>4.3973783480336</v>
       </c>
       <c r="O51" s="19" t="n">
@@ -13385,6 +14012,18 @@
         <f aca="false">B51/(2*PI()*r_w)*60*i_g</f>
         <v>9966.66666666667</v>
       </c>
+      <c r="V51" s="50" t="n">
+        <f aca="false">IF(B51=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B51))</f>
+        <v>11152.1739130435</v>
+      </c>
+      <c r="W51" s="19" t="n">
+        <f aca="false">MIN((J51-E51)/M_calc,(V51-E51)/(delta_m*M_calc))</f>
+        <v>3.75215066601662</v>
+      </c>
+      <c r="X51" s="19" t="n">
+        <f aca="false">X50+(B51-B50)/((W51+W50)/2)</f>
+        <v>8.81829961171913</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="49" t="n">
@@ -13435,11 +14074,11 @@
         <v>12515.7446808511</v>
       </c>
       <c r="M52" s="19" t="n">
-        <f aca="false">(K52-E52)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I52-E52)/M_calc,(G52-E52)/(delta_m*M_calc))</f>
         <v>4.26678042959766</v>
       </c>
       <c r="N52" s="19" t="n">
-        <f aca="false">(L52-E52)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J52-E52)/M_calc,(G52-E52)/(delta_m*M_calc))</f>
         <v>4.26678042959766</v>
       </c>
       <c r="O52" s="19" t="n">
@@ -13470,6 +14109,18 @@
         <f aca="false">B52/(2*PI()*r_w)*60*i_g</f>
         <v>10183.3333333333</v>
       </c>
+      <c r="V52" s="50" t="n">
+        <f aca="false">IF(B52=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B52))</f>
+        <v>10914.8936170213</v>
+      </c>
+      <c r="W52" s="19" t="n">
+        <f aca="false">MIN((J52-E52)/M_calc,(V52-E52)/(delta_m*M_calc))</f>
+        <v>3.63528099613424</v>
+      </c>
+      <c r="X52" s="19" t="n">
+        <f aca="false">X51+(B52-B51)/((W52+W51)/2)</f>
+        <v>9.19431361832031</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="49" t="n">
@@ -13520,11 +14171,11 @@
         <v>12255</v>
       </c>
       <c r="M53" s="19" t="n">
-        <f aca="false">(K53-E53)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I53-E53)/M_calc,(G53-E53)/(delta_m*M_calc))</f>
         <v>4.14015420556651</v>
       </c>
       <c r="N53" s="19" t="n">
-        <f aca="false">(L53-E53)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J53-E53)/M_calc,(G53-E53)/(delta_m*M_calc))</f>
         <v>4.14015420556651</v>
       </c>
       <c r="O53" s="19" t="n">
@@ -13555,6 +14206,18 @@
         <f aca="false">B53/(2*PI()*r_w)*60*i_g</f>
         <v>10400</v>
       </c>
+      <c r="V53" s="50" t="n">
+        <f aca="false">IF(B53=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B53))</f>
+        <v>10687.5</v>
+      </c>
+      <c r="W53" s="19" t="n">
+        <f aca="false">MIN((J53-E53)/M_calc,(V53-E53)/(delta_m*M_calc))</f>
+        <v>3.52181101030024</v>
+      </c>
+      <c r="X53" s="19" t="n">
+        <f aca="false">X52+(B53-B52)/((W53+W52)/2)</f>
+        <v>9.58242903939922</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="49" t="n">
@@ -13605,11 +14268,11 @@
         <v>12004.8979591837</v>
       </c>
       <c r="M54" s="19" t="n">
-        <f aca="false">(K54-E54)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I54-E54)/M_calc,(G54-E54)/(delta_m*M_calc))</f>
         <v>4.01722587506454</v>
       </c>
       <c r="N54" s="19" t="n">
-        <f aca="false">(L54-E54)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J54-E54)/M_calc,(G54-E54)/(delta_m*M_calc))</f>
         <v>4.01722587506454</v>
       </c>
       <c r="O54" s="19" t="n">
@@ -13640,6 +14303,18 @@
         <f aca="false">B54/(2*PI()*r_w)*60*i_g</f>
         <v>10616.6666666667</v>
       </c>
+      <c r="V54" s="50" t="n">
+        <f aca="false">IF(B54=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B54))</f>
+        <v>10469.387755102</v>
+      </c>
+      <c r="W54" s="19" t="n">
+        <f aca="false">MIN((J54-E54)/M_calc,(V54-E54)/(delta_m*M_calc))</f>
+        <v>3.41150192868125</v>
+      </c>
+      <c r="X54" s="19" t="n">
+        <f aca="false">X53+(B54-B53)/((W54+W53)/2)</f>
+        <v>9.98307124352651</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="49" t="n">
@@ -13690,11 +14365,11 @@
         <v>11764.8</v>
       </c>
       <c r="M55" s="19" t="n">
-        <f aca="false">(K55-E55)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I55-E55)/M_calc,(G55-E55)/(delta_m*M_calc))</f>
         <v>3.89774354128619</v>
       </c>
       <c r="N55" s="19" t="n">
-        <f aca="false">(L55-E55)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J55-E55)/M_calc,(G55-E55)/(delta_m*M_calc))</f>
         <v>3.89774354128619</v>
       </c>
       <c r="O55" s="19" t="n">
@@ -13725,6 +14400,18 @@
         <f aca="false">B55/(2*PI()*r_w)*60*i_g</f>
         <v>10833.3333333333</v>
       </c>
+      <c r="V55" s="50" t="n">
+        <f aca="false">IF(B55=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B55))</f>
+        <v>10260</v>
+      </c>
+      <c r="W55" s="19" t="n">
+        <f aca="false">MIN((J55-E55)/M_calc,(V55-E55)/(delta_m*M_calc))</f>
+        <v>3.30413407383057</v>
+      </c>
+      <c r="X55" s="19" t="n">
+        <f aca="false">X54+(B55-B54)/((W55+W54)/2)</f>
+        <v>10.3966996439846</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="49" t="n">
@@ -13775,11 +14462,11 @@
         <v>11534.1176470588</v>
       </c>
       <c r="M56" s="19" t="n">
-        <f aca="false">(K56-E56)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I56-E56)/M_calc,(G56-E56)/(delta_m*M_calc))</f>
         <v>3.78147506403811</v>
       </c>
       <c r="N56" s="19" t="n">
-        <f aca="false">(L56-E56)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J56-E56)/M_calc,(G56-E56)/(delta_m*M_calc))</f>
         <v>3.78147506403811</v>
       </c>
       <c r="O56" s="19" t="n">
@@ -13810,6 +14497,18 @@
         <f aca="false">B56/(2*PI()*r_w)*60*i_g</f>
         <v>11050</v>
       </c>
+      <c r="V56" s="50" t="n">
+        <f aca="false">IF(B56=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B56))</f>
+        <v>10058.8235294118</v>
+      </c>
+      <c r="W56" s="19" t="n">
+        <f aca="false">MIN((J56-E56)/M_calc,(V56-E56)/(delta_m*M_calc))</f>
+        <v>3.19950499790515</v>
+      </c>
+      <c r="X56" s="19" t="n">
+        <f aca="false">X55+(B56-B55)/((W56+W55)/2)</f>
+        <v>10.8238109499994</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="49" t="n">
@@ -13860,11 +14559,11 @@
         <v>11312.3076923077</v>
       </c>
       <c r="M57" s="19" t="n">
-        <f aca="false">(K57-E57)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I57-E57)/M_calc,(G57-E57)/(delta_m*M_calc))</f>
         <v>3.66820616006489</v>
       </c>
       <c r="N57" s="19" t="n">
-        <f aca="false">(L57-E57)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J57-E57)/M_calc,(G57-E57)/(delta_m*M_calc))</f>
         <v>3.66820616006489</v>
       </c>
       <c r="O57" s="19" t="n">
@@ -13895,6 +14594,18 @@
         <f aca="false">B57/(2*PI()*r_w)*60*i_g</f>
         <v>11266.6666666667</v>
       </c>
+      <c r="V57" s="50" t="n">
+        <f aca="false">IF(B57=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B57))</f>
+        <v>9865.38461538462</v>
+      </c>
+      <c r="W57" s="19" t="n">
+        <f aca="false">MIN((J57-E57)/M_calc,(V57-E57)/(delta_m*M_calc))</f>
+        <v>3.09742782597294</v>
+      </c>
+      <c r="X57" s="19" t="n">
+        <f aca="false">X56+(B57-B56)/((W57+W56)/2)</f>
+        <v>11.264942824115</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="49" t="n">
@@ -13945,11 +14656,11 @@
         <v>11098.8679245283</v>
       </c>
       <c r="M58" s="19" t="n">
-        <f aca="false">(K58-E58)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I58-E58)/M_calc,(G58-E58)/(delta_m*M_calc))</f>
         <v>3.55773871843228</v>
       </c>
       <c r="N58" s="19" t="n">
-        <f aca="false">(L58-E58)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J58-E58)/M_calc,(G58-E58)/(delta_m*M_calc))</f>
         <v>3.55773871843228</v>
       </c>
       <c r="O58" s="19" t="n">
@@ -13980,6 +14691,18 @@
         <f aca="false">B58/(2*PI()*r_w)*60*i_g</f>
         <v>11483.3333333333</v>
       </c>
+      <c r="V58" s="50" t="n">
+        <f aca="false">IF(B58=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B58))</f>
+        <v>9679.24528301887</v>
+      </c>
+      <c r="W58" s="19" t="n">
+        <f aca="false">MIN((J58-E58)/M_calc,(V58-E58)/(delta_m*M_calc))</f>
+        <v>2.99772978687037</v>
+      </c>
+      <c r="X58" s="19" t="n">
+        <f aca="false">X57+(B58-B57)/((W58+W57)/2)</f>
+        <v>11.7206780083742</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="49" t="n">
@@ -14030,11 +14753,11 @@
         <v>10893.3333333333</v>
       </c>
       <c r="M59" s="19" t="n">
-        <f aca="false">(K59-E59)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I59-E59)/M_calc,(G59-E59)/(delta_m*M_calc))</f>
         <v>3.44988930309007</v>
       </c>
       <c r="N59" s="19" t="n">
-        <f aca="false">(L59-E59)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J59-E59)/M_calc,(G59-E59)/(delta_m*M_calc))</f>
         <v>3.44988930309007</v>
       </c>
       <c r="O59" s="19" t="n">
@@ -14065,6 +14788,18 @@
         <f aca="false">B59/(2*PI()*r_w)*60*i_g</f>
         <v>11700</v>
       </c>
+      <c r="V59" s="50" t="n">
+        <f aca="false">IF(B59=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B59))</f>
+        <v>9500</v>
+      </c>
+      <c r="W59" s="19" t="n">
+        <f aca="false">MIN((J59-E59)/M_calc,(V59-E59)/(delta_m*M_calc))</f>
+        <v>2.90025090729783</v>
+      </c>
+      <c r="X59" s="19" t="n">
+        <f aca="false">X58+(B59-B58)/((W59+W58)/2)</f>
+        <v>12.1916489934987</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="49" t="n">
@@ -14115,11 +14850,11 @@
         <v>10695.2727272727</v>
       </c>
       <c r="M60" s="19" t="n">
-        <f aca="false">(K60-E60)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I60-E60)/M_calc,(G60-E60)/(delta_m*M_calc))</f>
         <v>3.34448781879169</v>
       </c>
       <c r="N60" s="19" t="n">
-        <f aca="false">(L60-E60)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J60-E60)/M_calc,(G60-E60)/(delta_m*M_calc))</f>
         <v>3.34448781879169</v>
       </c>
       <c r="O60" s="19" t="n">
@@ -14150,6 +14885,18 @@
         <f aca="false">B60/(2*PI()*r_w)*60*i_g</f>
         <v>11916.6666666667</v>
       </c>
+      <c r="V60" s="50" t="n">
+        <f aca="false">IF(B60=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B60))</f>
+        <v>9327.27272727273</v>
+      </c>
+      <c r="W60" s="19" t="n">
+        <f aca="false">MIN((J60-E60)/M_calc,(V60-E60)/(delta_m*M_calc))</f>
+        <v>2.80484284837749</v>
+      </c>
+      <c r="X60" s="19" t="n">
+        <f aca="false">X59+(B60-B59)/((W60+W59)/2)</f>
+        <v>12.6785433192956</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="49" t="n">
@@ -14200,11 +14947,11 @@
         <v>10504.2857142857</v>
       </c>
       <c r="M61" s="19" t="n">
-        <f aca="false">(K61-E61)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I61-E61)/M_calc,(G61-E61)/(delta_m*M_calc))</f>
         <v>3.24137631995102</v>
       </c>
       <c r="N61" s="19" t="n">
-        <f aca="false">(L61-E61)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J61-E61)/M_calc,(G61-E61)/(delta_m*M_calc))</f>
         <v>3.24137631995102</v>
       </c>
       <c r="O61" s="19" t="n">
@@ -14235,6 +14982,18 @@
         <f aca="false">B61/(2*PI()*r_w)*60*i_g</f>
         <v>12133.3333333333</v>
       </c>
+      <c r="V61" s="50" t="n">
+        <f aca="false">IF(B61=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B61))</f>
+        <v>9160.71428571429</v>
+      </c>
+      <c r="W61" s="19" t="n">
+        <f aca="false">MIN((J61-E61)/M_calc,(V61-E61)/(delta_m*M_calc))</f>
+        <v>2.71136786686565</v>
+      </c>
+      <c r="X61" s="19" t="n">
+        <f aca="false">X60+(B61-B60)/((W61+W60)/2)</f>
+        <v>13.1821096116604</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="49" t="n">
@@ -14285,11 +15044,11 @@
         <v>10320</v>
       </c>
       <c r="M62" s="19" t="n">
-        <f aca="false">(K62-E62)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I62-E62)/M_calc,(G62-E62)/(delta_m*M_calc))</f>
         <v>3.14040794488275</v>
       </c>
       <c r="N62" s="19" t="n">
-        <f aca="false">(L62-E62)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J62-E62)/M_calc,(G62-E62)/(delta_m*M_calc))</f>
         <v>3.14040794488275</v>
       </c>
       <c r="O62" s="19" t="n">
@@ -14320,6 +15079,18 @@
         <f aca="false">B62/(2*PI()*r_w)*60*i_g</f>
         <v>12350</v>
       </c>
+      <c r="V62" s="50" t="n">
+        <f aca="false">IF(B62=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B62))</f>
+        <v>9000</v>
+      </c>
+      <c r="W62" s="19" t="n">
+        <f aca="false">MIN((J62-E62)/M_calc,(V62-E62)/(delta_m*M_calc))</f>
+        <v>2.61969788571115</v>
+      </c>
+      <c r="X62" s="19" t="n">
+        <f aca="false">X61+(B62-B61)/((W62+W61)/2)</f>
+        <v>13.7031644826185</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="49" t="n">
@@ -14370,11 +15141,11 @@
         <v>10142.0689655172</v>
       </c>
       <c r="M63" s="19" t="n">
-        <f aca="false">(K63-E63)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I63-E63)/M_calc,(G63-E63)/(delta_m*M_calc))</f>
         <v>3.04144596029365</v>
       </c>
       <c r="N63" s="19" t="n">
-        <f aca="false">(L63-E63)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J63-E63)/M_calc,(G63-E63)/(delta_m*M_calc))</f>
         <v>3.04144596029365</v>
       </c>
       <c r="O63" s="19" t="n">
@@ -14405,6 +15176,18 @@
         <f aca="false">B63/(2*PI()*r_w)*60*i_g</f>
         <v>12566.6666666667</v>
       </c>
+      <c r="V63" s="50" t="n">
+        <f aca="false">IF(B63=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B63))</f>
+        <v>8844.8275862069</v>
+      </c>
+      <c r="W63" s="19" t="n">
+        <f aca="false">MIN((J63-E63)/M_calc,(V63-E63)/(delta_m*M_calc))</f>
+        <v>2.52971366076294</v>
+      </c>
+      <c r="X63" s="19" t="n">
+        <f aca="false">X62+(B63-B62)/((W63+W62)/2)</f>
+        <v>14.2426004458752</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="49" t="n">
@@ -14455,11 +15238,11 @@
         <v>9970.16949152543</v>
       </c>
       <c r="M64" s="19" t="n">
-        <f aca="false">(K64-E64)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I64-E64)/M_calc,(G64-E64)/(delta_m*M_calc))</f>
         <v>2.94436290294426</v>
       </c>
       <c r="N64" s="19" t="n">
-        <f aca="false">(L64-E64)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J64-E64)/M_calc,(G64-E64)/(delta_m*M_calc))</f>
         <v>2.94436290294426</v>
       </c>
       <c r="O64" s="19" t="n">
@@ -14490,6 +15273,18 @@
         <f aca="false">B64/(2*PI()*r_w)*60*i_g</f>
         <v>12783.3333333333</v>
       </c>
+      <c r="V64" s="50" t="n">
+        <f aca="false">IF(B64=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B64))</f>
+        <v>8694.91525423729</v>
+      </c>
+      <c r="W64" s="19" t="n">
+        <f aca="false">MIN((J64-E64)/M_calc,(V64-E64)/(delta_m*M_calc))</f>
+        <v>2.44130403221916</v>
+      </c>
+      <c r="X64" s="19" t="n">
+        <f aca="false">X63+(B64-B63)/((W64+W63)/2)</f>
+        <v>14.8013950326858</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="49" t="n">
@@ -14540,11 +15335,11 @@
         <v>9804</v>
       </c>
       <c r="M65" s="19" t="n">
-        <f aca="false">(K65-E65)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((I65-E65)/M_calc,(G65-E65)/(delta_m*M_calc))</f>
         <v>2.84903980714442</v>
       </c>
       <c r="N65" s="19" t="n">
-        <f aca="false">(L65-E65)/(delta_m*M_calc)</f>
+        <f aca="false">MIN((J65-E65)/M_calc,(G65-E65)/(delta_m*M_calc))</f>
         <v>2.84903980714442</v>
       </c>
       <c r="O65" s="19" t="n">
@@ -14575,10 +15370,22 @@
         <f aca="false">B65/(2*PI()*r_w)*60*i_g</f>
         <v>13000</v>
       </c>
+      <c r="V65" s="50" t="n">
+        <f aca="false">IF(B65=0,T_max*i_g*eta_t/r_w,MIN(T_max*i_g*eta_t/r_w,eta_t*P_cal*1000/B65))</f>
+        <v>8550</v>
+      </c>
+      <c r="W65" s="19" t="n">
+        <f aca="false">MIN((J65-E65)/M_calc,(V65-E65)/(delta_m*M_calc))</f>
+        <v>2.3543652509314</v>
+      </c>
+      <c r="X65" s="19" t="n">
+        <f aca="false">X64+(B65-B64)/((W65+W64)/2)</f>
+        <v>15.3806213332852</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:T2"/>
+    <mergeCell ref="A2:X2"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
